--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_2sep26_Wed.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_2sep26_Wed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F821D3-B37A-4448-A6AE-A53495CA5A37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BE67F3B-5CA9-406F-BF04-BF7873FEDCFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1019,7 +1019,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1191,18 +1191,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1218,37 +1206,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="22" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="22" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1612,7 +1569,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="2" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="3">
         <v>46258.375694444447</v>
       </c>
@@ -1626,7 +1583,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="4">
-        <v>1452</v>
+        <v>1465</v>
       </c>
       <c r="F2" s="4">
         <v>-0.29526883199999998</v>
@@ -1651,15 +1608,15 @@
       </c>
       <c r="M2" s="20">
         <f>ABS((D2*E2)-L2)</f>
-        <v>580</v>
+        <v>450</v>
       </c>
       <c r="N2" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B2, $C$2:$C$820, C2, $D$2:$D$820, D2, $E$2:$E$820, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N65" si="0">IF(COUNTIFS( $B$2:$B$820, B2, $C$2:$C$820, C2, $D$2:$D$820, D2, $E$2:$E$820, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
         <v>62</v>
       </c>
@@ -1694,12 +1651,12 @@
       <c r="L3" s="19"/>
       <c r="M3" s="19"/>
       <c r="N3" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B3, $C$2:$C$820, C3, $D$2:$D$820, D3, $E$2:$E$820, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O3" s="19"/>
     </row>
-    <row r="4" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
         <v>46261.375</v>
       </c>
@@ -1741,12 +1698,12 @@
         <v>300</v>
       </c>
       <c r="N4" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B4, $C$2:$C$820, C4, $D$2:$D$820, D4, $E$2:$E$820, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O4" s="20"/>
     </row>
-    <row r="5" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -1781,12 +1738,12 @@
       <c r="L5" s="19"/>
       <c r="M5" s="19"/>
       <c r="N5" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B5, $C$2:$C$820, C5, $D$2:$D$820, D5, $E$2:$E$820, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O5" s="19"/>
     </row>
-    <row r="6" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="6" t="s">
         <v>62</v>
       </c>
@@ -1819,12 +1776,12 @@
       <c r="L6" s="19"/>
       <c r="M6" s="19"/>
       <c r="N6" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B6, $C$2:$C$820, C6, $D$2:$D$820, D6, $E$2:$E$820, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O6" s="19"/>
     </row>
-    <row r="7" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -1857,12 +1814,12 @@
       <c r="L7" s="19"/>
       <c r="M7" s="19"/>
       <c r="N7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B7, $C$2:$C$820, C7, $D$2:$D$820, D7, $E$2:$E$820, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O7" s="19"/>
     </row>
-    <row r="8" spans="1:15" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:15" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="3">
         <v>46252.6875</v>
       </c>
@@ -1897,12 +1854,12 @@
       <c r="L8" s="19"/>
       <c r="M8" s="19"/>
       <c r="N8" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B8, $C$2:$C$820, C8, $D$2:$D$820, D8, $E$2:$E$820, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O8" s="19"/>
     </row>
-    <row r="9" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="6" t="s">
         <v>62</v>
       </c>
@@ -1935,12 +1892,12 @@
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
       <c r="N9" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B9, $C$2:$C$820, C9, $D$2:$D$820, D9, $E$2:$E$820, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O9" s="19"/>
     </row>
-    <row r="10" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="6" t="s">
         <v>62</v>
       </c>
@@ -1973,7 +1930,7 @@
       <c r="L10" s="19"/>
       <c r="M10" s="19"/>
       <c r="N10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B10, $C$2:$C$820, C10, $D$2:$D$820, D10, $E$2:$E$820, E10) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O10" s="19"/>
@@ -2011,12 +1968,12 @@
       <c r="L11" s="19"/>
       <c r="M11" s="19"/>
       <c r="N11" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B11, $C$2:$C$820, C11, $D$2:$D$820, D11, $E$2:$E$820, E11) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O11" s="19"/>
     </row>
-    <row r="12" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="6" t="s">
         <v>62</v>
       </c>
@@ -2049,12 +2006,12 @@
       <c r="L12" s="19"/>
       <c r="M12" s="19"/>
       <c r="N12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B12, $C$2:$C$820, C12, $D$2:$D$820, D12, $E$2:$E$820, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O12" s="19"/>
     </row>
-    <row r="13" spans="1:15" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:15" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="6" t="s">
         <v>62</v>
       </c>
@@ -2087,12 +2044,12 @@
       <c r="L13" s="19"/>
       <c r="M13" s="19"/>
       <c r="N13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B13, $C$2:$C$820, C13, $D$2:$D$820, D13, $E$2:$E$820, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O13" s="19"/>
     </row>
-    <row r="14" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="6" t="s">
         <v>62</v>
       </c>
@@ -2127,12 +2084,12 @@
       <c r="L14" s="19"/>
       <c r="M14" s="19"/>
       <c r="N14" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B14, $C$2:$C$820, C14, $D$2:$D$820, D14, $E$2:$E$820, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O14" s="19"/>
     </row>
-    <row r="15" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="6" t="s">
         <v>62</v>
       </c>
@@ -2165,12 +2122,12 @@
       <c r="L15" s="19"/>
       <c r="M15" s="19"/>
       <c r="N15" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B15, $C$2:$C$820, C15, $D$2:$D$820, D15, $E$2:$E$820, E15) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O15" s="19"/>
     </row>
-    <row r="16" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="6" t="s">
         <v>62</v>
       </c>
@@ -2203,12 +2160,12 @@
       <c r="L16" s="19"/>
       <c r="M16" s="19"/>
       <c r="N16" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B16, $C$2:$C$820, C16, $D$2:$D$820, D16, $E$2:$E$820, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O16" s="19"/>
     </row>
-    <row r="17" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -2250,12 +2207,12 @@
         <v>250</v>
       </c>
       <c r="N17" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B17, $C$2:$C$820, C17, $D$2:$D$820, D17, $E$2:$E$820, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O17" s="20"/>
     </row>
-    <row r="18" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3">
         <v>46252.6875</v>
       </c>
@@ -2290,12 +2247,12 @@
       <c r="L18" s="19"/>
       <c r="M18" s="19"/>
       <c r="N18" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B18, $C$2:$C$820, C18, $D$2:$D$820, D18, $E$2:$E$820, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O18" s="19"/>
     </row>
-    <row r="19" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -2330,12 +2287,12 @@
       <c r="L19" s="19"/>
       <c r="M19" s="19"/>
       <c r="N19" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B19, $C$2:$C$820, C19, $D$2:$D$820, D19, $E$2:$E$820, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O19" s="19"/>
     </row>
-    <row r="20" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="3">
         <v>46252.645833333336</v>
       </c>
@@ -2370,12 +2327,12 @@
       <c r="L20" s="19"/>
       <c r="M20" s="19"/>
       <c r="N20" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B20, $C$2:$C$820, C20, $D$2:$D$820, D20, $E$2:$E$820, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O20" s="19"/>
     </row>
-    <row r="21" spans="1:15" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:15" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3">
         <v>46267.375439814816</v>
       </c>
@@ -2417,7 +2374,7 @@
         <v>300</v>
       </c>
       <c r="N21" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B21, $C$2:$C$820, C21, $D$2:$D$820, D21, $E$2:$E$820, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O21" s="20"/>
@@ -2457,12 +2414,12 @@
       <c r="L22" s="19"/>
       <c r="M22" s="19"/>
       <c r="N22" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B22, $C$2:$C$820, C22, $D$2:$D$820, D22, $E$2:$E$820, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O22" s="19"/>
     </row>
-    <row r="23" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="6" t="s">
         <v>62</v>
       </c>
@@ -2495,12 +2452,12 @@
       <c r="L23" s="19"/>
       <c r="M23" s="19"/>
       <c r="N23" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B23, $C$2:$C$820, C23, $D$2:$D$820, D23, $E$2:$E$820, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O23" s="19"/>
     </row>
-    <row r="24" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -2533,12 +2490,12 @@
       <c r="L24" s="19"/>
       <c r="M24" s="19"/>
       <c r="N24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B24, $C$2:$C$820, C24, $D$2:$D$820, D24, $E$2:$E$820, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O24" s="19"/>
     </row>
-    <row r="25" spans="1:15" s="48" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:15" s="48" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="6" t="s">
         <v>62</v>
       </c>
@@ -2571,12 +2528,12 @@
       <c r="L25" s="19"/>
       <c r="M25" s="19"/>
       <c r="N25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B25, $C$2:$C$820, C25, $D$2:$D$820, D25, $E$2:$E$820, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O25" s="19"/>
     </row>
-    <row r="26" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="3">
         <v>46266.375</v>
       </c>
@@ -2618,12 +2575,12 @@
         <v>320</v>
       </c>
       <c r="N26" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B26, $C$2:$C$820, C26, $D$2:$D$820, D26, $E$2:$E$820, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O26" s="20"/>
     </row>
-    <row r="27" spans="1:15" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:15" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="6" t="s">
         <v>62</v>
       </c>
@@ -2656,12 +2613,12 @@
       <c r="L27" s="19"/>
       <c r="M27" s="19"/>
       <c r="N27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B27, $C$2:$C$820, C27, $D$2:$D$820, D27, $E$2:$E$820, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O27" s="19"/>
     </row>
-    <row r="28" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="6" t="s">
         <v>62</v>
       </c>
@@ -2694,12 +2651,12 @@
       <c r="L28" s="19"/>
       <c r="M28" s="19"/>
       <c r="N28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B28, $C$2:$C$820, C28, $D$2:$D$820, D28, $E$2:$E$820, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O28" s="19"/>
     </row>
-    <row r="29" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="6" t="s">
         <v>62</v>
       </c>
@@ -2732,12 +2689,12 @@
       <c r="L29" s="19"/>
       <c r="M29" s="19"/>
       <c r="N29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B29, $C$2:$C$820, C29, $D$2:$D$820, D29, $E$2:$E$820, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O29" s="19"/>
     </row>
-    <row r="30" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -2770,12 +2727,12 @@
       <c r="L30" s="19"/>
       <c r="M30" s="19"/>
       <c r="N30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B30, $C$2:$C$820, C30, $D$2:$D$820, D30, $E$2:$E$820, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O30" s="19"/>
     </row>
-    <row r="31" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="6" t="s">
         <v>62</v>
       </c>
@@ -2808,12 +2765,12 @@
       <c r="L31" s="19"/>
       <c r="M31" s="19"/>
       <c r="N31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B31, $C$2:$C$820, C31, $D$2:$D$820, D31, $E$2:$E$820, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O31" s="19"/>
     </row>
-    <row r="32" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -2846,12 +2803,12 @@
       <c r="L32" s="19"/>
       <c r="M32" s="19"/>
       <c r="N32" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B32, $C$2:$C$820, C32, $D$2:$D$820, D32, $E$2:$E$820, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O32" s="19"/>
     </row>
-    <row r="33" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -2886,12 +2843,12 @@
       <c r="L33" s="19"/>
       <c r="M33" s="19"/>
       <c r="N33" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B33, $C$2:$C$820, C33, $D$2:$D$820, D33, $E$2:$E$820, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O33" s="19"/>
     </row>
-    <row r="34" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="6" t="s">
         <v>62</v>
       </c>
@@ -2924,12 +2881,12 @@
       <c r="L34" s="19"/>
       <c r="M34" s="19"/>
       <c r="N34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B34, $C$2:$C$820, C34, $D$2:$D$820, D34, $E$2:$E$820, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O34" s="19"/>
     </row>
-    <row r="35" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="6" t="s">
         <v>62</v>
       </c>
@@ -2962,12 +2919,12 @@
       <c r="L35" s="19"/>
       <c r="M35" s="19"/>
       <c r="N35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B35, $C$2:$C$820, C35, $D$2:$D$820, D35, $E$2:$E$820, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O35" s="19"/>
     </row>
-    <row r="36" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -3002,12 +2959,12 @@
       <c r="L36" s="19"/>
       <c r="M36" s="19"/>
       <c r="N36" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B36, $C$2:$C$820, C36, $D$2:$D$820, D36, $E$2:$E$820, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O36" s="19"/>
     </row>
-    <row r="37" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="6" t="s">
         <v>62</v>
       </c>
@@ -3040,12 +2997,12 @@
       <c r="L37" s="19"/>
       <c r="M37" s="19"/>
       <c r="N37" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B37, $C$2:$C$820, C37, $D$2:$D$820, D37, $E$2:$E$820, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O37" s="19"/>
     </row>
-    <row r="38" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="3">
         <v>46252.6875</v>
       </c>
@@ -3078,12 +3035,12 @@
       <c r="L38" s="19"/>
       <c r="M38" s="19"/>
       <c r="N38" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B38, $C$2:$C$820, C38, $D$2:$D$820, D38, $E$2:$E$820, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O38" s="19"/>
     </row>
-    <row r="39" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="3">
         <v>46261.375</v>
       </c>
@@ -3125,12 +3082,12 @@
         <v>300</v>
       </c>
       <c r="N39" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B39, $C$2:$C$820, C39, $D$2:$D$820, D39, $E$2:$E$820, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O39" s="20"/>
     </row>
-    <row r="40" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="3">
         <v>46031.4375</v>
       </c>
@@ -3168,12 +3125,12 @@
         <v>3156</v>
       </c>
       <c r="N40" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B40, $C$2:$C$820, C40, $D$2:$D$820, D40, $E$2:$E$820, E40) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O40" s="20"/>
     </row>
-    <row r="41" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="6" t="s">
         <v>62</v>
       </c>
@@ -3206,12 +3163,12 @@
       <c r="L41" s="19"/>
       <c r="M41" s="19"/>
       <c r="N41" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B41, $C$2:$C$820, C41, $D$2:$D$820, D41, $E$2:$E$820, E41) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O41" s="19"/>
     </row>
-    <row r="42" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="3">
         <v>46252.6875</v>
       </c>
@@ -3246,12 +3203,12 @@
       <c r="L42" s="19"/>
       <c r="M42" s="19"/>
       <c r="N42" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B42, $C$2:$C$820, C42, $D$2:$D$820, D42, $E$2:$E$820, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O42" s="19"/>
     </row>
-    <row r="43" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="6" t="s">
         <v>62</v>
       </c>
@@ -3284,12 +3241,12 @@
       <c r="L43" s="19"/>
       <c r="M43" s="19"/>
       <c r="N43" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B43, $C$2:$C$820, C43, $D$2:$D$820, D43, $E$2:$E$820, E43) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O43" s="19"/>
     </row>
-    <row r="44" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="6" t="s">
         <v>62</v>
       </c>
@@ -3324,12 +3281,12 @@
       <c r="L44" s="19"/>
       <c r="M44" s="19"/>
       <c r="N44" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B44, $C$2:$C$820, C44, $D$2:$D$820, D44, $E$2:$E$820, E44) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O44" s="19"/>
     </row>
-    <row r="45" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="6" t="s">
         <v>62</v>
       </c>
@@ -3362,12 +3319,12 @@
       <c r="L45" s="19"/>
       <c r="M45" s="19"/>
       <c r="N45" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B45, $C$2:$C$820, C45, $D$2:$D$820, D45, $E$2:$E$820, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O45" s="19"/>
     </row>
-    <row r="46" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="6" t="s">
         <v>62</v>
       </c>
@@ -3400,12 +3357,12 @@
       <c r="L46" s="19"/>
       <c r="M46" s="19"/>
       <c r="N46" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B46, $C$2:$C$820, C46, $D$2:$D$820, D46, $E$2:$E$820, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O46" s="19"/>
     </row>
-    <row r="47" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -3438,12 +3395,12 @@
       <c r="L47" s="19"/>
       <c r="M47" s="19"/>
       <c r="N47" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B47, $C$2:$C$820, C47, $D$2:$D$820, D47, $E$2:$E$820, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O47" s="19"/>
     </row>
-    <row r="48" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="43">
         <v>46255</v>
       </c>
@@ -3485,12 +3442,12 @@
         <v>442</v>
       </c>
       <c r="N48" s="42" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B48, $C$2:$C$820, C48, $D$2:$D$820, D48, $E$2:$E$820, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O48" s="41"/>
     </row>
-    <row r="49" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3">
         <v>46262.457638888889</v>
       </c>
@@ -3532,12 +3489,12 @@
         <v>222.75</v>
       </c>
       <c r="N49" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B49, $C$2:$C$820, C49, $D$2:$D$820, D49, $E$2:$E$820, E49) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O49" s="20"/>
     </row>
-    <row r="50" spans="1:15" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:15" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -3570,12 +3527,12 @@
       <c r="L50" s="19"/>
       <c r="M50" s="19"/>
       <c r="N50" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B50, $C$2:$C$820, C50, $D$2:$D$820, D50, $E$2:$E$820, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O50" s="19"/>
     </row>
-    <row r="51" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="3">
         <v>46260.375</v>
       </c>
@@ -3617,12 +3574,12 @@
         <v>300</v>
       </c>
       <c r="N51" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B51, $C$2:$C$820, C51, $D$2:$D$820, D51, $E$2:$E$820, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O51" s="20"/>
     </row>
-    <row r="52" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="6" t="s">
         <v>62</v>
       </c>
@@ -3657,12 +3614,12 @@
       <c r="L52" s="19"/>
       <c r="M52" s="19"/>
       <c r="N52" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B52, $C$2:$C$820, C52, $D$2:$D$820, D52, $E$2:$E$820, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O52" s="19"/>
     </row>
-    <row r="53" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="22">
         <v>46255</v>
       </c>
@@ -3704,12 +3661,12 @@
         <v>400</v>
       </c>
       <c r="N53" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B53, $C$2:$C$820, C53, $D$2:$D$820, D53, $E$2:$E$820, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O53" s="20"/>
     </row>
-    <row r="54" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="3">
         <v>46261.375</v>
       </c>
@@ -3751,12 +3708,12 @@
         <v>300</v>
       </c>
       <c r="N54" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B54, $C$2:$C$820, C54, $D$2:$D$820, D54, $E$2:$E$820, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O54" s="20"/>
     </row>
-    <row r="55" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="6" t="s">
         <v>62</v>
       </c>
@@ -3789,12 +3746,12 @@
       <c r="L55" s="19"/>
       <c r="M55" s="19"/>
       <c r="N55" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B55, $C$2:$C$820, C55, $D$2:$D$820, D55, $E$2:$E$820, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O55" s="19"/>
     </row>
-    <row r="56" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="6" t="s">
         <v>62</v>
       </c>
@@ -3827,12 +3784,12 @@
       <c r="L56" s="19"/>
       <c r="M56" s="19"/>
       <c r="N56" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B56, $C$2:$C$820, C56, $D$2:$D$820, D56, $E$2:$E$820, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O56" s="19"/>
     </row>
-    <row r="57" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="3">
         <v>46252.6875</v>
       </c>
@@ -3865,12 +3822,12 @@
       <c r="L57" s="19"/>
       <c r="M57" s="19"/>
       <c r="N57" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B57, $C$2:$C$820, C57, $D$2:$D$820, D57, $E$2:$E$820, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O57" s="19"/>
     </row>
-    <row r="58" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="6" t="s">
         <v>62</v>
       </c>
@@ -3903,12 +3860,12 @@
       <c r="L58" s="19"/>
       <c r="M58" s="19"/>
       <c r="N58" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B58, $C$2:$C$820, C58, $D$2:$D$820, D58, $E$2:$E$820, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O58" s="19"/>
     </row>
-    <row r="59" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="6" t="s">
         <v>62</v>
       </c>
@@ -3943,12 +3900,12 @@
       <c r="L59" s="19"/>
       <c r="M59" s="19"/>
       <c r="N59" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B59, $C$2:$C$820, C59, $D$2:$D$820, D59, $E$2:$E$820, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O59" s="19"/>
     </row>
-    <row r="60" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="3">
         <v>46252.6875</v>
       </c>
@@ -3983,12 +3940,12 @@
       <c r="L60" s="19"/>
       <c r="M60" s="19"/>
       <c r="N60" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B60, $C$2:$C$820, C60, $D$2:$D$820, D60, $E$2:$E$820, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O60" s="19"/>
     </row>
-    <row r="61" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="6" t="s">
         <v>62</v>
       </c>
@@ -4021,12 +3978,12 @@
       <c r="L61" s="19"/>
       <c r="M61" s="19"/>
       <c r="N61" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B61, $C$2:$C$820, C61, $D$2:$D$820, D61, $E$2:$E$820, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O61" s="19"/>
     </row>
-    <row r="62" spans="1:15" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:15" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="6" t="s">
         <v>62</v>
       </c>
@@ -4061,12 +4018,12 @@
       <c r="L62" s="19"/>
       <c r="M62" s="19"/>
       <c r="N62" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B62, $C$2:$C$820, C62, $D$2:$D$820, D62, $E$2:$E$820, E62) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O62" s="19"/>
     </row>
-    <row r="63" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:15" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="6" t="s">
         <v>62</v>
       </c>
@@ -4099,12 +4056,12 @@
       <c r="L63" s="19"/>
       <c r="M63" s="19"/>
       <c r="N63" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B63, $C$2:$C$820, C63, $D$2:$D$820, D63, $E$2:$E$820, E63) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O63" s="19"/>
     </row>
-    <row r="64" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="6" t="s">
         <v>62</v>
       </c>
@@ -4137,12 +4094,12 @@
       <c r="L64" s="19"/>
       <c r="M64" s="19"/>
       <c r="N64" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B64, $C$2:$C$820, C64, $D$2:$D$820, D64, $E$2:$E$820, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O64" s="19"/>
     </row>
-    <row r="65" spans="1:15" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:15" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" s="6" t="s">
         <v>62</v>
       </c>
@@ -4175,12 +4132,12 @@
       <c r="L65" s="19"/>
       <c r="M65" s="19"/>
       <c r="N65" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B65, $C$2:$C$820, C65, $D$2:$D$820, D65, $E$2:$E$820, E65) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O65" s="19"/>
     </row>
-    <row r="66" spans="1:15" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:15" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="6" t="s">
         <v>62</v>
       </c>
@@ -4213,12 +4170,12 @@
       <c r="L66" s="19"/>
       <c r="M66" s="19"/>
       <c r="N66" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B66, $C$2:$C$820, C66, $D$2:$D$820, D66, $E$2:$E$820, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N66:N129" si="1">IF(COUNTIFS( $B$2:$B$820, B66, $C$2:$C$820, C66, $D$2:$D$820, D66, $E$2:$E$820, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O66" s="19"/>
     </row>
-    <row r="67" spans="1:15" ht="16.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:15" ht="16.25" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="3">
         <v>46252.6875</v>
       </c>
@@ -4253,12 +4210,12 @@
       <c r="L67" s="19"/>
       <c r="M67" s="19"/>
       <c r="N67" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B67, $C$2:$C$820, C67, $D$2:$D$820, D67, $E$2:$E$820, E67) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O67" s="19"/>
     </row>
-    <row r="68" spans="1:15" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:15" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -4291,12 +4248,12 @@
       <c r="L68" s="19"/>
       <c r="M68" s="19"/>
       <c r="N68" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B68, $C$2:$C$820, C68, $D$2:$D$820, D68, $E$2:$E$820, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O68" s="19"/>
     </row>
-    <row r="69" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:15" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="6" t="s">
         <v>62</v>
       </c>
@@ -4329,12 +4286,12 @@
       <c r="L69" s="19"/>
       <c r="M69" s="19"/>
       <c r="N69" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B69, $C$2:$C$820, C69, $D$2:$D$820, D69, $E$2:$E$820, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O69" s="19"/>
     </row>
-    <row r="70" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="6" t="s">
         <v>62</v>
       </c>
@@ -4369,12 +4326,12 @@
       <c r="L70" s="19"/>
       <c r="M70" s="19"/>
       <c r="N70" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B70, $C$2:$C$820, C70, $D$2:$D$820, D70, $E$2:$E$820, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O70" s="19"/>
     </row>
-    <row r="71" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="6" t="s">
         <v>62</v>
       </c>
@@ -4409,12 +4366,12 @@
       <c r="L71" s="19"/>
       <c r="M71" s="19"/>
       <c r="N71" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B71, $C$2:$C$820, C71, $D$2:$D$820, D71, $E$2:$E$820, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O71" s="19"/>
     </row>
-    <row r="72" spans="1:15" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:15" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="6" t="s">
         <v>62</v>
       </c>
@@ -4447,12 +4404,12 @@
       <c r="L72" s="19"/>
       <c r="M72" s="19"/>
       <c r="N72" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B72, $C$2:$C$820, C72, $D$2:$D$820, D72, $E$2:$E$820, E72) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O72" s="19"/>
     </row>
-    <row r="73" spans="1:15" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:15" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="3">
         <v>46252.688194444447</v>
       </c>
@@ -4485,12 +4442,12 @@
       <c r="L73" s="19"/>
       <c r="M73" s="19"/>
       <c r="N73" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B73, $C$2:$C$820, C73, $D$2:$D$820, D73, $E$2:$E$820, E73) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O73" s="19"/>
     </row>
-    <row r="74" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="6" t="s">
         <v>62</v>
       </c>
@@ -4523,12 +4480,12 @@
       <c r="L74" s="19"/>
       <c r="M74" s="19"/>
       <c r="N74" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B74, $C$2:$C$820, C74, $D$2:$D$820, D74, $E$2:$E$820, E74) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O74" s="19"/>
     </row>
-    <row r="75" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="3">
         <v>46258.601388888892</v>
       </c>
@@ -4570,11 +4527,11 @@
         <v>300</v>
       </c>
       <c r="N75" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B75, $C$2:$C$820, C75, $D$2:$D$820, D75, $E$2:$E$820, E75) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="6" t="s">
         <v>62</v>
       </c>
@@ -4607,12 +4564,12 @@
       <c r="L76" s="19"/>
       <c r="M76" s="19"/>
       <c r="N76" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B76, $C$2:$C$820, C76, $D$2:$D$820, D76, $E$2:$E$820, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O76" s="19"/>
     </row>
-    <row r="77" spans="1:15" s="30" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:15" s="30" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="6" t="s">
         <v>62</v>
       </c>
@@ -4647,12 +4604,12 @@
       <c r="L77" s="19"/>
       <c r="M77" s="19"/>
       <c r="N77" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B77, $C$2:$C$820, C77, $D$2:$D$820, D77, $E$2:$E$820, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O77" s="19"/>
     </row>
-    <row r="78" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="6" t="s">
         <v>62</v>
       </c>
@@ -4685,12 +4642,12 @@
       <c r="L78" s="19"/>
       <c r="M78" s="19"/>
       <c r="N78" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B78, $C$2:$C$820, C78, $D$2:$D$820, D78, $E$2:$E$820, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O78" s="19"/>
     </row>
-    <row r="79" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:15" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="3">
         <v>46252.6875</v>
       </c>
@@ -4725,12 +4682,12 @@
       <c r="L79" s="19"/>
       <c r="M79" s="19"/>
       <c r="N79" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B79, $C$2:$C$820, C79, $D$2:$D$820, D79, $E$2:$E$820, E79) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O79" s="19"/>
     </row>
-    <row r="80" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="6" t="s">
         <v>62</v>
       </c>
@@ -4763,12 +4720,12 @@
       <c r="L80" s="19"/>
       <c r="M80" s="19"/>
       <c r="N80" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B80, $C$2:$C$820, C80, $D$2:$D$820, D80, $E$2:$E$820, E80) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O80" s="19"/>
     </row>
-    <row r="81" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="6" t="s">
         <v>62</v>
       </c>
@@ -4801,12 +4758,12 @@
       <c r="L81" s="19"/>
       <c r="M81" s="19"/>
       <c r="N81" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B81, $C$2:$C$820, C81, $D$2:$D$820, D81, $E$2:$E$820, E81) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O81" s="19"/>
     </row>
-    <row r="82" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="3">
         <v>46254.375</v>
       </c>
@@ -4843,12 +4800,12 @@
       <c r="L82" s="19"/>
       <c r="M82" s="19"/>
       <c r="N82" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B82, $C$2:$C$820, C82, $D$2:$D$820, D82, $E$2:$E$820, E82) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O82" s="19"/>
     </row>
-    <row r="83" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="6" t="s">
         <v>62</v>
       </c>
@@ -4881,12 +4838,12 @@
       <c r="L83" s="19"/>
       <c r="M83" s="19"/>
       <c r="N83" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B83, $C$2:$C$820, C83, $D$2:$D$820, D83, $E$2:$E$820, E83) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O83" s="19"/>
     </row>
-    <row r="84" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="6" t="s">
         <v>62</v>
       </c>
@@ -4919,12 +4876,12 @@
       <c r="L84" s="19"/>
       <c r="M84" s="19"/>
       <c r="N84" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B84, $C$2:$C$820, C84, $D$2:$D$820, D84, $E$2:$E$820, E84) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O84" s="19"/>
     </row>
-    <row r="85" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:15" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A85" s="6" t="s">
         <v>62</v>
       </c>
@@ -4959,12 +4916,12 @@
       <c r="L85" s="19"/>
       <c r="M85" s="19"/>
       <c r="N85" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B85, $C$2:$C$820, C85, $D$2:$D$820, D85, $E$2:$E$820, E85) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O85" s="19"/>
     </row>
-    <row r="86" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="6" t="s">
         <v>62</v>
       </c>
@@ -4997,12 +4954,12 @@
       <c r="L86" s="19"/>
       <c r="M86" s="19"/>
       <c r="N86" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B86, $C$2:$C$820, C86, $D$2:$D$820, D86, $E$2:$E$820, E86) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O86" s="19"/>
     </row>
-    <row r="87" spans="1:15" s="21" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:15" s="21" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A87" s="6" t="s">
         <v>62</v>
       </c>
@@ -5035,12 +4992,12 @@
       <c r="L87" s="19"/>
       <c r="M87" s="19"/>
       <c r="N87" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B87, $C$2:$C$820, C87, $D$2:$D$820, D87, $E$2:$E$820, E87) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O87" s="19"/>
     </row>
-    <row r="88" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A88" s="6" t="s">
         <v>62</v>
       </c>
@@ -5075,12 +5032,12 @@
       <c r="L88" s="19"/>
       <c r="M88" s="19"/>
       <c r="N88" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B88, $C$2:$C$820, C88, $D$2:$D$820, D88, $E$2:$E$820, E88) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O88" s="19"/>
     </row>
-    <row r="89" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A89" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -5113,12 +5070,12 @@
       <c r="L89" s="19"/>
       <c r="M89" s="19"/>
       <c r="N89" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B89, $C$2:$C$820, C89, $D$2:$D$820, D89, $E$2:$E$820, E89) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O89" s="19"/>
     </row>
-    <row r="90" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:15" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A90" s="6" t="s">
         <v>62</v>
       </c>
@@ -5151,12 +5108,12 @@
       <c r="L90" s="19"/>
       <c r="M90" s="19"/>
       <c r="N90" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B90, $C$2:$C$820, C90, $D$2:$D$820, D90, $E$2:$E$820, E90) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O90" s="19"/>
     </row>
-    <row r="91" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A91" s="6" t="s">
         <v>62</v>
       </c>
@@ -5189,12 +5146,12 @@
       <c r="L91" s="19"/>
       <c r="M91" s="19"/>
       <c r="N91" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B91, $C$2:$C$820, C91, $D$2:$D$820, D91, $E$2:$E$820, E91) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O91" s="19"/>
     </row>
-    <row r="92" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="6" t="s">
         <v>62</v>
       </c>
@@ -5229,11 +5186,11 @@
       <c r="L92" s="19"/>
       <c r="M92" s="19"/>
       <c r="N92" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B92, $C$2:$C$820, C92, $D$2:$D$820, D92, $E$2:$E$820, E92) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="6" t="s">
         <v>62</v>
       </c>
@@ -5266,12 +5223,12 @@
       <c r="L93" s="19"/>
       <c r="M93" s="19"/>
       <c r="N93" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B93, $C$2:$C$820, C93, $D$2:$D$820, D93, $E$2:$E$820, E93) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O93" s="19"/>
     </row>
-    <row r="94" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:15" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="6" t="s">
         <v>62</v>
       </c>
@@ -5304,11 +5261,11 @@
       <c r="L94" s="19"/>
       <c r="M94" s="19"/>
       <c r="N94" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B94, $C$2:$C$820, C94, $D$2:$D$820, D94, $E$2:$E$820, E94) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="95" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="6" t="s">
         <v>62</v>
       </c>
@@ -5341,12 +5298,12 @@
       <c r="L95" s="19"/>
       <c r="M95" s="19"/>
       <c r="N95" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B95, $C$2:$C$820, C95, $D$2:$D$820, D95, $E$2:$E$820, E95) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O95" s="19"/>
     </row>
-    <row r="96" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A96" s="3">
         <v>46252.688194444447</v>
       </c>
@@ -5379,12 +5336,12 @@
       <c r="L96" s="19"/>
       <c r="M96" s="19"/>
       <c r="N96" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B96, $C$2:$C$820, C96, $D$2:$D$820, D96, $E$2:$E$820, E96) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O96" s="19"/>
     </row>
-    <row r="97" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A97" s="6" t="s">
         <v>62</v>
       </c>
@@ -5417,11 +5374,11 @@
       <c r="L97" s="19"/>
       <c r="M97" s="19"/>
       <c r="N97" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B97, $C$2:$C$820, C97, $D$2:$D$820, D97, $E$2:$E$820, E97) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15" s="39" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" s="39" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="6" t="s">
         <v>62</v>
       </c>
@@ -5454,12 +5411,12 @@
       <c r="L98" s="19"/>
       <c r="M98" s="19"/>
       <c r="N98" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B98, $C$2:$C$820, C98, $D$2:$D$820, D98, $E$2:$E$820, E98) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O98" s="19"/>
     </row>
-    <row r="99" spans="1:15" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:15" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="6" t="s">
         <v>62</v>
       </c>
@@ -5494,7 +5451,7 @@
       <c r="L99" s="19"/>
       <c r="M99" s="19"/>
       <c r="N99" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B99, $C$2:$C$820, C99, $D$2:$D$820, D99, $E$2:$E$820, E99) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5530,11 +5487,11 @@
         <v>117</v>
       </c>
       <c r="N100" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B100, $C$2:$C$820, C100, $D$2:$D$820, D100, $E$2:$E$820, E100) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="6" t="s">
         <v>62</v>
       </c>
@@ -5567,7 +5524,7 @@
       <c r="L101" s="19"/>
       <c r="M101" s="19"/>
       <c r="N101" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B101, $C$2:$C$820, C101, $D$2:$D$820, D101, $E$2:$E$820, E101) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5603,7 +5560,7 @@
         <v>117</v>
       </c>
       <c r="N102" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B102, $C$2:$C$820, C102, $D$2:$D$820, D102, $E$2:$E$820, E102) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5649,7 +5606,7 @@
         <v>300</v>
       </c>
       <c r="N103" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B103, $C$2:$C$820, C103, $D$2:$D$820, D103, $E$2:$E$820, E103) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5695,7 +5652,7 @@
         <v>520</v>
       </c>
       <c r="N104" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B104, $C$2:$C$820, C104, $D$2:$D$820, D104, $E$2:$E$820, E104) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5734,7 +5691,7 @@
       <c r="L105" s="20"/>
       <c r="M105" s="20"/>
       <c r="N105" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B105, $C$2:$C$820, C105, $D$2:$D$820, D105, $E$2:$E$820, E105) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O105" s="20"/>
@@ -5777,11 +5734,11 @@
         <v>12600</v>
       </c>
       <c r="M106" s="47">
-        <f>ABS((D106*E106)-L106)</f>
+        <f t="shared" ref="M106:M122" si="2">ABS((D106*E106)-L106)</f>
         <v>200</v>
       </c>
       <c r="N106" s="49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B106, $C$2:$C$820, C106, $D$2:$D$820, D106, $E$2:$E$820, E106) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O106" s="47"/>
@@ -5824,11 +5781,11 @@
         <v>12510</v>
       </c>
       <c r="M107" s="47">
-        <f>ABS((D107*E107)-L107)</f>
+        <f t="shared" si="2"/>
         <v>290</v>
       </c>
       <c r="N107" s="49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B107, $C$2:$C$820, C107, $D$2:$D$820, D107, $E$2:$E$820, E107) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O107" s="47"/>
@@ -5871,11 +5828,11 @@
         <v>8220</v>
       </c>
       <c r="M108" s="20">
-        <f>ABS((D108*E108)-L108)</f>
+        <f t="shared" si="2"/>
         <v>360</v>
       </c>
       <c r="N108" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B108, $C$2:$C$820, C108, $D$2:$D$820, D108, $E$2:$E$820, E108) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5917,11 +5874,11 @@
         <v>20010</v>
       </c>
       <c r="M109" s="20">
-        <f>ABS((D109*E109)-L109)</f>
+        <f t="shared" si="2"/>
         <v>450</v>
       </c>
       <c r="N109" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B109, $C$2:$C$820, C109, $D$2:$D$820, D109, $E$2:$E$820, E109) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5963,11 +5920,11 @@
         <v>3560</v>
       </c>
       <c r="M110" s="47">
-        <f>ABS((D110*E110)-L110)</f>
+        <f t="shared" si="2"/>
         <v>175</v>
       </c>
       <c r="N110" s="49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B110, $C$2:$C$820, C110, $D$2:$D$820, D110, $E$2:$E$820, E110) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O110" s="47"/>
@@ -6010,11 +5967,11 @@
         <v>3510</v>
       </c>
       <c r="M111" s="47">
-        <f>ABS((D111*E111)-L111)</f>
+        <f t="shared" si="2"/>
         <v>225</v>
       </c>
       <c r="N111" s="48" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B111, $C$2:$C$820, C111, $D$2:$D$820, D111, $E$2:$E$820, E111) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O111" s="47"/>
@@ -6057,11 +6014,11 @@
         <v>8625</v>
       </c>
       <c r="M112" s="20">
-        <f>ABS((D112*E112)-L112)</f>
+        <f t="shared" si="2"/>
         <v>375</v>
       </c>
       <c r="N112" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B112, $C$2:$C$820, C112, $D$2:$D$820, D112, $E$2:$E$820, E112) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6103,11 +6060,11 @@
         <v>9270</v>
       </c>
       <c r="M113" s="20">
-        <f>ABS((D113*E113)-L113)</f>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N113" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B113, $C$2:$C$820, C113, $D$2:$D$820, D113, $E$2:$E$820, E113) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6149,11 +6106,11 @@
         <v>20260</v>
       </c>
       <c r="M114" s="20">
-        <f>ABS((D114*E114)-L114)</f>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N114" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B114, $C$2:$C$820, C114, $D$2:$D$820, D114, $E$2:$E$820, E114) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6195,11 +6152,11 @@
         <v>8810</v>
       </c>
       <c r="M115" s="20">
-        <f>ABS((D115*E115)-L115)</f>
+        <f t="shared" si="2"/>
         <v>650</v>
       </c>
       <c r="N115" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B115, $C$2:$C$820, C115, $D$2:$D$820, D115, $E$2:$E$820, E115) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6241,11 +6198,11 @@
         <v>4842</v>
       </c>
       <c r="M116" s="20">
-        <f>ABS((D116*E116)-L116)</f>
+        <f t="shared" si="2"/>
         <v>540</v>
       </c>
       <c r="N116" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B116, $C$2:$C$820, C116, $D$2:$D$820, D116, $E$2:$E$820, E116) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6287,11 +6244,11 @@
         <v>8320</v>
       </c>
       <c r="M117" s="20">
-        <f>ABS((D117*E117)-L117)</f>
+        <f t="shared" si="2"/>
         <v>650</v>
       </c>
       <c r="N117" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B117, $C$2:$C$820, C117, $D$2:$D$820, D117, $E$2:$E$820, E117) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6333,11 +6290,11 @@
         <v>5755</v>
       </c>
       <c r="M118" s="47">
-        <f>ABS((D118*E118)-L118)</f>
+        <f t="shared" si="2"/>
         <v>275</v>
       </c>
       <c r="N118" s="49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B118, $C$2:$C$820, C118, $D$2:$D$820, D118, $E$2:$E$820, E118) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O118" s="47"/>
@@ -6380,11 +6337,11 @@
         <v>5805</v>
       </c>
       <c r="M119" s="47">
-        <f>ABS((D119*E119)-L119)</f>
+        <f t="shared" si="2"/>
         <v>225</v>
       </c>
       <c r="N119" s="49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B119, $C$2:$C$820, C119, $D$2:$D$820, D119, $E$2:$E$820, E119) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O119" s="47"/>
@@ -6427,11 +6384,11 @@
         <v>26145</v>
       </c>
       <c r="M120" s="20">
-        <f>ABS((D120*E120)-L120)</f>
+        <f t="shared" si="2"/>
         <v>765</v>
       </c>
       <c r="N120" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B120, $C$2:$C$820, C120, $D$2:$D$820, D120, $E$2:$E$820, E120) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6473,11 +6430,11 @@
         <v>14440</v>
       </c>
       <c r="M121" s="20">
-        <f>ABS((D121*E121)-L121)</f>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N121" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B121, $C$2:$C$820, C121, $D$2:$D$820, D121, $E$2:$E$820, E121) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O121" s="20"/>
@@ -6520,11 +6477,11 @@
         <v>12600</v>
       </c>
       <c r="M122" s="20">
-        <f>ABS((D122*E122)-L122)</f>
+        <f t="shared" si="2"/>
         <v>360</v>
       </c>
       <c r="N122" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B122, $C$2:$C$820, C122, $D$2:$D$820, D122, $E$2:$E$820, E122) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6558,7 +6515,7 @@
       </c>
       <c r="J123" s="23"/>
       <c r="N123" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B123, $C$2:$C$820, C123, $D$2:$D$820, D123, $E$2:$E$820, E123) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6600,11 +6557,11 @@
         <v>32900</v>
       </c>
       <c r="M124" s="20">
-        <f>ABS((D124*E124)-L124)</f>
+        <f t="shared" ref="M124:M136" si="3">ABS((D124*E124)-L124)</f>
         <v>1000</v>
       </c>
       <c r="N124" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B124, $C$2:$C$820, C124, $D$2:$D$820, D124, $E$2:$E$820, E124) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -6646,11 +6603,11 @@
         <v>33200</v>
       </c>
       <c r="M125" s="20">
-        <f>ABS((D125*E125)-L125)</f>
+        <f t="shared" si="3"/>
         <v>700</v>
       </c>
       <c r="N125" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B125, $C$2:$C$820, C125, $D$2:$D$820, D125, $E$2:$E$820, E125) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O125" s="20"/>
@@ -6693,11 +6650,11 @@
         <v>10300</v>
       </c>
       <c r="M126" s="20">
-        <f>ABS((D126*E126)-L126)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N126" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B126, $C$2:$C$820, C126, $D$2:$D$820, D126, $E$2:$E$820, E126) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6739,11 +6696,11 @@
         <v>25300</v>
       </c>
       <c r="M127" s="20">
-        <f>ABS((D127*E127)-L127)</f>
+        <f t="shared" si="3"/>
         <v>650</v>
       </c>
       <c r="N127" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B127, $C$2:$C$820, C127, $D$2:$D$820, D127, $E$2:$E$820, E127) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6785,11 +6742,11 @@
         <v>12480</v>
       </c>
       <c r="M128" s="20">
-        <f>ABS((D128*E128)-L128)</f>
+        <f t="shared" si="3"/>
         <v>495</v>
       </c>
       <c r="N128" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B128, $C$2:$C$820, C128, $D$2:$D$820, D128, $E$2:$E$820, E128) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6821,7 +6778,7 @@
       <c r="I129" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J129" s="62" t="s">
+      <c r="J129" s="33" t="s">
         <v>118</v>
       </c>
       <c r="K129" s="33" t="s">
@@ -6831,11 +6788,11 @@
         <v>8420</v>
       </c>
       <c r="M129" s="33">
-        <f>ABS((D129*E129)-L129)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N129" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B129, $C$2:$C$820, C129, $D$2:$D$820, D129, $E$2:$E$820, E129) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O129" s="33" t="s">
@@ -6870,7 +6827,7 @@
       <c r="I130" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J130" s="59" t="s">
+      <c r="J130" s="20" t="s">
         <v>117</v>
       </c>
       <c r="K130" s="20" t="s">
@@ -6880,11 +6837,11 @@
         <v>5940</v>
       </c>
       <c r="M130" s="20">
-        <f>ABS((D130*E130)-L130)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N130" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B130, $C$2:$C$820, C130, $D$2:$D$820, D130, $E$2:$E$820, E130) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N130:N193" si="4">IF(COUNTIFS( $B$2:$B$820, B130, $C$2:$C$820, C130, $D$2:$D$820, D130, $E$2:$E$820, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O130" s="20"/>
@@ -6917,7 +6874,7 @@
       <c r="I131" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J131" s="61" t="s">
+      <c r="J131" s="47" t="s">
         <v>118</v>
       </c>
       <c r="K131" s="47" t="s">
@@ -6927,11 +6884,11 @@
         <v>7578</v>
       </c>
       <c r="M131" s="47">
-        <f>ABS((D131*E131)-L131)</f>
+        <f t="shared" si="3"/>
         <v>294</v>
       </c>
       <c r="N131" s="48" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B131, $C$2:$C$820, C131, $D$2:$D$820, D131, $E$2:$E$820, E131) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Duplicate</v>
       </c>
       <c r="O131" s="47"/>
@@ -6964,7 +6921,7 @@
       <c r="I132" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J132" s="61" t="s">
+      <c r="J132" s="47" t="s">
         <v>118</v>
       </c>
       <c r="K132" s="47" t="s">
@@ -6974,11 +6931,11 @@
         <v>7578</v>
       </c>
       <c r="M132" s="47">
-        <f>ABS((D132*E132)-L132)</f>
+        <f t="shared" si="3"/>
         <v>294</v>
       </c>
       <c r="N132" s="49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B132, $C$2:$C$820, C132, $D$2:$D$820, D132, $E$2:$E$820, E132) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Duplicate</v>
       </c>
       <c r="O132" s="47"/>
@@ -7021,11 +6978,11 @@
         <v>4968</v>
       </c>
       <c r="M133" s="20">
-        <f>ABS((D133*E133)-L133)</f>
+        <f t="shared" si="3"/>
         <v>280</v>
       </c>
       <c r="N133" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B133, $C$2:$C$820, C133, $D$2:$D$820, D133, $E$2:$E$820, E133) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O133" s="20"/>
@@ -7058,7 +7015,7 @@
       <c r="I134" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J134" s="59" t="s">
+      <c r="J134" s="20" t="s">
         <v>117</v>
       </c>
       <c r="K134" s="20" t="s">
@@ -7068,11 +7025,11 @@
         <v>18800</v>
       </c>
       <c r="M134" s="20">
-        <f>ABS((D134*E134)-L134)</f>
+        <f t="shared" si="3"/>
         <v>500</v>
       </c>
       <c r="N134" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B134, $C$2:$C$820, C134, $D$2:$D$820, D134, $E$2:$E$820, E134) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O134" s="20"/>
@@ -7115,11 +7072,11 @@
         <v>16755</v>
       </c>
       <c r="M135" s="20">
-        <f>ABS((D135*E135)-L135)</f>
+        <f t="shared" si="3"/>
         <v>295</v>
       </c>
       <c r="N135" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B135, $C$2:$C$820, C135, $D$2:$D$820, D135, $E$2:$E$820, E135) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O135" s="20"/>
@@ -7152,7 +7109,7 @@
       <c r="I136" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J136" s="59" t="s">
+      <c r="J136" s="20" t="s">
         <v>118</v>
       </c>
       <c r="K136" s="20" t="s">
@@ -7162,51 +7119,49 @@
         <v>25780</v>
       </c>
       <c r="M136" s="20">
-        <f>ABS((D136*E136)-L136)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N136" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B136, $C$2:$C$820, C136, $D$2:$D$820, D136, $E$2:$E$820, E136) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O136" s="20"/>
     </row>
-    <row r="137" spans="1:15" s="76" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A137" s="68">
+    <row r="137" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A137" s="13">
         <v>46252.635416666664</v>
       </c>
-      <c r="B137" s="69" t="s">
+      <c r="B137" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C137" s="69" t="s">
-        <v>7</v>
-      </c>
-      <c r="D137" s="69">
-        <v>8</v>
-      </c>
-      <c r="E137" s="69">
+      <c r="C137" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D137" s="10">
+        <v>8</v>
+      </c>
+      <c r="E137" s="10">
         <v>2448</v>
       </c>
-      <c r="F137" s="70">
+      <c r="F137" s="4">
         <v>4.615384615</v>
       </c>
-      <c r="G137" s="71" t="s">
+      <c r="G137" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="H137" s="72">
+      <c r="H137" s="5">
         <v>2340</v>
       </c>
-      <c r="I137" s="73" t="s">
-        <v>8</v>
-      </c>
-      <c r="J137" s="74"/>
-      <c r="K137" s="75"/>
-      <c r="L137" s="75"/>
-      <c r="M137" s="75"/>
-      <c r="N137" s="76" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B137, $C$2:$C$820, C137, $D$2:$D$820, D137, $E$2:$E$820, E137) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
+      <c r="I137" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J137" s="54"/>
+      <c r="N137" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v>Unique</v>
+      </c>
+      <c r="O137" s="12"/>
     </row>
     <row r="138" spans="1:15" s="49" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A138" s="3">
@@ -7236,7 +7191,7 @@
       <c r="I138" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J138" s="59" t="s">
+      <c r="J138" s="20" t="s">
         <v>117</v>
       </c>
       <c r="K138" s="20" t="s">
@@ -7250,7 +7205,7 @@
         <v>525</v>
       </c>
       <c r="N138" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B138, $C$2:$C$820, C138, $D$2:$D$820, D138, $E$2:$E$820, E138) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O138" s="20"/>
@@ -7283,12 +7238,12 @@
       <c r="I139" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J139" s="60"/>
+      <c r="J139" s="54"/>
       <c r="K139" s="20"/>
       <c r="L139" s="20"/>
       <c r="M139" s="20"/>
       <c r="N139" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B139, $C$2:$C$820, C139, $D$2:$D$820, D139, $E$2:$E$820, E139) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O139" s="20"/>
@@ -7323,7 +7278,7 @@
       </c>
       <c r="J140" s="54"/>
       <c r="N140" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B140, $C$2:$C$820, C140, $D$2:$D$820, D140, $E$2:$E$820, E140) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7355,7 +7310,7 @@
       <c r="I141" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J141" s="59" t="s">
+      <c r="J141" s="20" t="s">
         <v>117</v>
       </c>
       <c r="K141" s="20" t="s">
@@ -7369,7 +7324,7 @@
         <v>650</v>
       </c>
       <c r="N141" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B141, $C$2:$C$820, C141, $D$2:$D$820, D141, $E$2:$E$820, E141) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7401,7 +7356,7 @@
       <c r="I142" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J142" s="59" t="s">
+      <c r="J142" s="20" t="s">
         <v>118</v>
       </c>
       <c r="K142" s="20" t="s">
@@ -7415,7 +7370,7 @@
         <v>300</v>
       </c>
       <c r="N142" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B142, $C$2:$C$820, C142, $D$2:$D$820, D142, $E$2:$E$820, E142) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7454,7 +7409,7 @@
       <c r="L143" s="20"/>
       <c r="M143" s="20"/>
       <c r="N143" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B143, $C$2:$C$820, C143, $D$2:$D$820, D143, $E$2:$E$820, E143) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O143" s="20"/>
@@ -7487,7 +7442,7 @@
       <c r="I144" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J144" s="59" t="s">
+      <c r="J144" s="20" t="s">
         <v>117</v>
       </c>
       <c r="K144" s="20" t="s">
@@ -7501,7 +7456,7 @@
         <v>300</v>
       </c>
       <c r="N144" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B144, $C$2:$C$820, C144, $D$2:$D$820, D144, $E$2:$E$820, E144) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O144" s="20"/>
@@ -7548,7 +7503,7 @@
         <v>400</v>
       </c>
       <c r="N145" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B145, $C$2:$C$820, C145, $D$2:$D$820, D145, $E$2:$E$820, E145) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7584,7 +7539,7 @@
         <v>118</v>
       </c>
       <c r="N146" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B146, $C$2:$C$820, C146, $D$2:$D$820, D146, $E$2:$E$820, E146) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7616,11 +7571,11 @@
       <c r="I147" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J147" s="60" t="s">
+      <c r="J147" s="54" t="s">
         <v>117</v>
       </c>
       <c r="N147" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B147, $C$2:$C$820, C147, $D$2:$D$820, D147, $E$2:$E$820, E147) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7652,7 +7607,7 @@
       <c r="I148" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J148" s="59" t="s">
+      <c r="J148" s="20" t="s">
         <v>117</v>
       </c>
       <c r="K148" s="20" t="s">
@@ -7666,7 +7621,7 @@
         <v>500</v>
       </c>
       <c r="N148" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B148, $C$2:$C$820, C148, $D$2:$D$820, D148, $E$2:$E$820, E148) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7698,7 +7653,7 @@
       <c r="I149" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J149" s="59" t="s">
+      <c r="J149" s="20" t="s">
         <v>117</v>
       </c>
       <c r="K149" s="20" t="s">
@@ -7712,7 +7667,7 @@
         <v>340</v>
       </c>
       <c r="N149" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B149, $C$2:$C$820, C149, $D$2:$D$820, D149, $E$2:$E$820, E149) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7758,24 +7713,24 @@
         <v>1567.5</v>
       </c>
       <c r="N150" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B150, $C$2:$C$820, C150, $D$2:$D$820, D150, $E$2:$E$820, E150) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
     <row r="151" spans="1:15" s="30" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A151" s="65" t="s">
+      <c r="A151" s="61" t="s">
         <v>62</v>
       </c>
-      <c r="B151" s="66" t="s">
+      <c r="B151" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="C151" s="65" t="s">
-        <v>7</v>
-      </c>
-      <c r="D151" s="65">
+      <c r="C151" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="D151" s="61">
         <v>40</v>
       </c>
-      <c r="E151" s="67">
+      <c r="E151" s="63">
         <v>229</v>
       </c>
       <c r="F151" s="8">
@@ -7797,7 +7752,7 @@
       <c r="L151" s="33"/>
       <c r="M151" s="33"/>
       <c r="N151" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B151, $C$2:$C$820, C151, $D$2:$D$820, D151, $E$2:$E$820, E151) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O151" s="30" t="s">
@@ -7842,11 +7797,11 @@
         <v>5905</v>
       </c>
       <c r="M152" s="20">
-        <f>ABS((D152*E152)-L152)</f>
+        <f t="shared" ref="M152:M158" si="5">ABS((D152*E152)-L152)</f>
         <v>275</v>
       </c>
       <c r="N152" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B152, $C$2:$C$820, C152, $D$2:$D$820, D152, $E$2:$E$820, E152) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7888,11 +7843,11 @@
         <v>10510</v>
       </c>
       <c r="M153" s="20">
-        <f>ABS((D153*E153)-L153)</f>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N153" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B153, $C$2:$C$820, C153, $D$2:$D$820, D153, $E$2:$E$820, E153) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7934,11 +7889,11 @@
         <v>5154</v>
       </c>
       <c r="M154" s="20">
-        <f>ABS((D154*E154)-L154)</f>
+        <f t="shared" si="5"/>
         <v>270</v>
       </c>
       <c r="N154" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B154, $C$2:$C$820, C154, $D$2:$D$820, D154, $E$2:$E$820, E154) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7980,11 +7935,11 @@
         <v>8570</v>
       </c>
       <c r="M155" s="20">
-        <f>ABS((D155*E155)-L155)</f>
+        <f t="shared" si="5"/>
         <v>650</v>
       </c>
       <c r="N155" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B155, $C$2:$C$820, C155, $D$2:$D$820, D155, $E$2:$E$820, E155) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8026,11 +7981,11 @@
         <v>26180</v>
       </c>
       <c r="M156" s="20">
-        <f>ABS((D156*E156)-L156)</f>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N156" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B156, $C$2:$C$820, C156, $D$2:$D$820, D156, $E$2:$E$820, E156) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8053,10 +8008,10 @@
       <c r="F157" s="36">
         <v>6.2967795100000004</v>
       </c>
-      <c r="G157" s="63" t="s">
+      <c r="G157" s="59" t="s">
         <v>81</v>
       </c>
-      <c r="H157" s="64">
+      <c r="H157" s="60">
         <v>1456.3</v>
       </c>
       <c r="I157" s="35" t="s">
@@ -8072,11 +8027,11 @@
         <v>15050</v>
       </c>
       <c r="M157" s="37">
-        <f>ABS((D157*E157)-L157)</f>
+        <f t="shared" si="5"/>
         <v>430</v>
       </c>
       <c r="N157" s="38" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B157, $C$2:$C$820, C157, $D$2:$D$820, D157, $E$2:$E$820, E157) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O157" s="37"/>
@@ -8119,11 +8074,11 @@
         <v>3005</v>
       </c>
       <c r="M158" s="20">
-        <f>ABS((D158*E158)-L158)</f>
+        <f t="shared" si="5"/>
         <v>240</v>
       </c>
       <c r="N158" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B158, $C$2:$C$820, C158, $D$2:$D$820, D158, $E$2:$E$820, E158) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8159,57 +8114,56 @@
         <v>118</v>
       </c>
       <c r="N159" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B159, $C$2:$C$820, C159, $D$2:$D$820, D159, $E$2:$E$820, E159) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O159" s="12"/>
     </row>
-    <row r="160" spans="1:15" s="76" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A160" s="77">
+    <row r="160" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A160" s="3">
         <v>46262.375</v>
       </c>
-      <c r="B160" s="73" t="s">
+      <c r="B160" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C160" s="73" t="s">
-        <v>7</v>
-      </c>
-      <c r="D160" s="70">
-        <v>10</v>
-      </c>
-      <c r="E160" s="70">
+      <c r="C160" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D160" s="4">
+        <v>10</v>
+      </c>
+      <c r="E160" s="4">
         <v>2660</v>
       </c>
-      <c r="F160" s="70">
+      <c r="F160" s="4">
         <v>6.5278333999999996</v>
       </c>
-      <c r="G160" s="71" t="s">
+      <c r="G160" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="H160" s="72">
+      <c r="H160" s="5">
         <v>2497</v>
       </c>
-      <c r="I160" s="73" t="s">
-        <v>8</v>
-      </c>
-      <c r="J160" s="75" t="s">
+      <c r="I160" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J160" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="K160" s="75" t="s">
+      <c r="K160" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="L160" s="75">
+      <c r="L160" s="20">
         <v>26300</v>
       </c>
-      <c r="M160" s="75">
-        <f>ABS((D160*E160)-L160)</f>
+      <c r="M160" s="20">
+        <f t="shared" ref="M160:M167" si="6">ABS((D160*E160)-L160)</f>
         <v>300</v>
       </c>
-      <c r="N160" s="76" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B160, $C$2:$C$820, C160, $D$2:$D$820, D160, $E$2:$E$820, E160) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O160" s="75"/>
+      <c r="N160" s="12" t="str">
+        <f t="shared" si="4"/>
+        <v>Unique</v>
+      </c>
     </row>
     <row r="161" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A161" s="3">
@@ -8239,7 +8193,7 @@
       <c r="I161" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J161" s="59" t="s">
+      <c r="J161" s="20" t="s">
         <v>117</v>
       </c>
       <c r="K161" s="20" t="s">
@@ -8249,11 +8203,11 @@
         <v>34100</v>
       </c>
       <c r="M161" s="20">
-        <f>ABS((D161*E161)-L161)</f>
+        <f t="shared" si="6"/>
         <v>700</v>
       </c>
       <c r="N161" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B161, $C$2:$C$820, C161, $D$2:$D$820, D161, $E$2:$E$820, E161) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8295,11 +8249,11 @@
         <v>4120</v>
       </c>
       <c r="M162" s="20">
-        <f>ABS((D162*E162)-L162)</f>
+        <f t="shared" si="6"/>
         <v>270</v>
       </c>
       <c r="N162" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B162, $C$2:$C$820, C162, $D$2:$D$820, D162, $E$2:$E$820, E162) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8341,11 +8295,11 @@
         <v>5820</v>
       </c>
       <c r="M163" s="20">
-        <f>ABS((D163*E163)-L163)</f>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N163" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B163, $C$2:$C$820, C163, $D$2:$D$820, D163, $E$2:$E$820, E163) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8387,11 +8341,11 @@
         <v>4080</v>
       </c>
       <c r="M164" s="20">
-        <f>ABS((D164*E164)-L164)</f>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N164" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B164, $C$2:$C$820, C164, $D$2:$D$820, D164, $E$2:$E$820, E164) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8423,7 +8377,7 @@
       <c r="I165" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J165" s="59" t="s">
+      <c r="J165" s="20" t="s">
         <v>117</v>
       </c>
       <c r="K165" s="20" t="s">
@@ -8433,11 +8387,11 @@
         <v>17150</v>
       </c>
       <c r="M165" s="20">
-        <f>ABS((D165*E165)-L165)</f>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N165" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B165, $C$2:$C$820, C165, $D$2:$D$820, D165, $E$2:$E$820, E165) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8479,11 +8433,11 @@
         <v>5120</v>
       </c>
       <c r="M166" s="20">
-        <f>ABS((D166*E166)-L166)</f>
+        <f t="shared" si="6"/>
         <v>260</v>
       </c>
       <c r="N166" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B166, $C$2:$C$820, C166, $D$2:$D$820, D166, $E$2:$E$820, E166) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8525,11 +8479,11 @@
         <v>13030</v>
       </c>
       <c r="M167" s="20">
-        <f>ABS((D167*E167)-L167)</f>
+        <f t="shared" si="6"/>
         <v>370</v>
       </c>
       <c r="N167" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B167, $C$2:$C$820, C167, $D$2:$D$820, D167, $E$2:$E$820, E167) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8565,7 +8519,7 @@
         <v>41</v>
       </c>
       <c r="N168" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B168, $C$2:$C$820, C168, $D$2:$D$820, D168, $E$2:$E$820, E168) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O168" s="12"/>
@@ -8607,7 +8561,7 @@
       <c r="L169" s="19"/>
       <c r="M169" s="19"/>
       <c r="N169" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B169, $C$2:$C$820, C169, $D$2:$D$820, D169, $E$2:$E$820, E169) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8653,7 +8607,7 @@
         <v>300</v>
       </c>
       <c r="N170" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B170, $C$2:$C$820, C170, $D$2:$D$820, D170, $E$2:$E$820, E170) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8699,7 +8653,7 @@
         <v>150</v>
       </c>
       <c r="N171" s="48" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B171, $C$2:$C$820, C171, $D$2:$D$820, D171, $E$2:$E$820, E171) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Duplicate</v>
       </c>
       <c r="O171" s="47"/>
@@ -8746,7 +8700,7 @@
         <v>250</v>
       </c>
       <c r="N172" s="49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B172, $C$2:$C$820, C172, $D$2:$D$820, D172, $E$2:$E$820, E172) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Duplicate</v>
       </c>
       <c r="O172" s="47"/>
@@ -8781,7 +8735,7 @@
       </c>
       <c r="J173" s="54"/>
       <c r="N173" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B173, $C$2:$C$820, C173, $D$2:$D$820, D173, $E$2:$E$820, E173) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O173" s="12"/>
@@ -8828,7 +8782,7 @@
         <v>700</v>
       </c>
       <c r="N174" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B174, $C$2:$C$820, C174, $D$2:$D$820, D174, $E$2:$E$820, E174) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8864,7 +8818,7 @@
         <v>41</v>
       </c>
       <c r="N175" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B175, $C$2:$C$820, C175, $D$2:$D$820, D175, $E$2:$E$820, E175) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8910,7 +8864,7 @@
         <v>260</v>
       </c>
       <c r="N176" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B176, $C$2:$C$820, C176, $D$2:$D$820, D176, $E$2:$E$820, E176) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8944,7 +8898,7 @@
       </c>
       <c r="J177" s="54"/>
       <c r="N177" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B177, $C$2:$C$820, C177, $D$2:$D$820, D177, $E$2:$E$820, E177) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O177" s="12"/>
@@ -8981,7 +8935,7 @@
         <v>117</v>
       </c>
       <c r="N178" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B178, $C$2:$C$820, C178, $D$2:$D$820, D178, $E$2:$E$820, E178) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O178" s="12"/>
@@ -9018,7 +8972,7 @@
         <v>118</v>
       </c>
       <c r="N179" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B179, $C$2:$C$820, C179, $D$2:$D$820, D179, $E$2:$E$820, E179) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9054,7 +9008,7 @@
         <v>118</v>
       </c>
       <c r="N180" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B180, $C$2:$C$820, C180, $D$2:$D$820, D180, $E$2:$E$820, E180) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O180" s="12"/>
@@ -9101,7 +9055,7 @@
         <v>800</v>
       </c>
       <c r="N181" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B181, $C$2:$C$820, C181, $D$2:$D$820, D181, $E$2:$E$820, E181) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9137,7 +9091,7 @@
         <v>156</v>
       </c>
       <c r="N182" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B182, $C$2:$C$820, C182, $D$2:$D$820, D182, $E$2:$E$820, E182) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9173,7 +9127,7 @@
         <v>204</v>
       </c>
       <c r="N183" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B183, $C$2:$C$820, C183, $D$2:$D$820, D183, $E$2:$E$820, E183) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O183" s="12"/>
@@ -9206,14 +9160,14 @@
       <c r="I184" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J184" s="60" t="s">
+      <c r="J184" s="54" t="s">
         <v>118</v>
       </c>
       <c r="K184" s="20" t="s">
         <v>145</v>
       </c>
       <c r="N184" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B184, $C$2:$C$820, C184, $D$2:$D$820, D184, $E$2:$E$820, E184) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9259,7 +9213,7 @@
         <v>527.5</v>
       </c>
       <c r="N185" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B185, $C$2:$C$820, C185, $D$2:$D$820, D185, $E$2:$E$820, E185) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9298,7 +9252,7 @@
         <v>143</v>
       </c>
       <c r="N186" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B186, $C$2:$C$820, C186, $D$2:$D$820, D186, $E$2:$E$820, E186) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9344,7 +9298,7 @@
         <v>250</v>
       </c>
       <c r="N187" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B187, $C$2:$C$820, C187, $D$2:$D$820, D187, $E$2:$E$820, E187) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9380,7 +9334,7 @@
         <v>118</v>
       </c>
       <c r="N188" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B188, $C$2:$C$820, C188, $D$2:$D$820, D188, $E$2:$E$820, E188) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9426,7 +9380,7 @@
         <v>700</v>
       </c>
       <c r="N189" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B189, $C$2:$C$820, C189, $D$2:$D$820, D189, $E$2:$E$820, E189) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9460,7 +9414,7 @@
       </c>
       <c r="J190" s="54"/>
       <c r="N190" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B190, $C$2:$C$820, C190, $D$2:$D$820, D190, $E$2:$E$820, E190) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9506,7 +9460,7 @@
         <v>300</v>
       </c>
       <c r="N191" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B191, $C$2:$C$820, C191, $D$2:$D$820, D191, $E$2:$E$820, E191) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9540,11 +9494,11 @@
       </c>
       <c r="J192" s="54"/>
       <c r="N192" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B192, $C$2:$C$820, C192, $D$2:$D$820, D192, $E$2:$E$820, E192) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="193" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="4"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A193" s="3">
         <v>46265.415277777778</v>
       </c>
@@ -9573,7 +9527,7 @@
         <v>8</v>
       </c>
       <c r="J193" s="20" t="s">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="K193" s="20" t="s">
         <v>211</v>
@@ -9586,11 +9540,11 @@
         <v>285</v>
       </c>
       <c r="N193" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B193, $C$2:$C$820, C193, $D$2:$D$820, D193, $E$2:$E$820, E193) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="194" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="4"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="194" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A194" s="3">
         <v>46266.375</v>
       </c>
@@ -9632,7 +9586,7 @@
         <v>726</v>
       </c>
       <c r="N194" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B194, $C$2:$C$820, C194, $D$2:$D$820, D194, $E$2:$E$820, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N194:N257" si="7">IF(COUNTIFS( $B$2:$B$820, B194, $C$2:$C$820, C194, $D$2:$D$820, D194, $E$2:$E$820, E194) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -9678,7 +9632,7 @@
         <v>460</v>
       </c>
       <c r="N195" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B195, $C$2:$C$820, C195, $D$2:$D$820, D195, $E$2:$E$820, E195) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9724,7 +9678,7 @@
         <v>320</v>
       </c>
       <c r="N196" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B196, $C$2:$C$820, C196, $D$2:$D$820, D196, $E$2:$E$820, E196) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9770,7 +9724,7 @@
         <v>448</v>
       </c>
       <c r="N197" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B197, $C$2:$C$820, C197, $D$2:$D$820, D197, $E$2:$E$820, E197) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9804,7 +9758,7 @@
       </c>
       <c r="J198" s="54"/>
       <c r="N198" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B198, $C$2:$C$820, C198, $D$2:$D$820, D198, $E$2:$E$820, E198) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O198" s="12"/>
@@ -9851,7 +9805,7 @@
         <v>650</v>
       </c>
       <c r="N199" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B199, $C$2:$C$820, C199, $D$2:$D$820, D199, $E$2:$E$820, E199) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9897,7 +9851,7 @@
         <v>650</v>
       </c>
       <c r="N200" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B200, $C$2:$C$820, C200, $D$2:$D$820, D200, $E$2:$E$820, E200) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9931,7 +9885,7 @@
       </c>
       <c r="J201" s="54"/>
       <c r="N201" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B201, $C$2:$C$820, C201, $D$2:$D$820, D201, $E$2:$E$820, E201) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9977,7 +9931,7 @@
         <v>250</v>
       </c>
       <c r="N202" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B202, $C$2:$C$820, C202, $D$2:$D$820, D202, $E$2:$E$820, E202) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10023,7 +9977,7 @@
         <v>300</v>
       </c>
       <c r="N203" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B203, $C$2:$C$820, C203, $D$2:$D$820, D203, $E$2:$E$820, E203) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10057,7 +10011,7 @@
       </c>
       <c r="J204" s="54"/>
       <c r="N204" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B204, $C$2:$C$820, C204, $D$2:$D$820, D204, $E$2:$E$820, E204) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O204" s="12"/>
@@ -10092,7 +10046,7 @@
       </c>
       <c r="J205" s="54"/>
       <c r="N205" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B205, $C$2:$C$820, C205, $D$2:$D$820, D205, $E$2:$E$820, E205) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O205" s="12"/>
@@ -10127,7 +10081,7 @@
       </c>
       <c r="J206" s="54"/>
       <c r="N206" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B206, $C$2:$C$820, C206, $D$2:$D$820, D206, $E$2:$E$820, E206) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O206" s="12"/>
@@ -10162,7 +10116,7 @@
       </c>
       <c r="J207" s="54"/>
       <c r="N207" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B207, $C$2:$C$820, C207, $D$2:$D$820, D207, $E$2:$E$820, E207) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O207" s="12"/>
@@ -10199,7 +10153,7 @@
         <v>117</v>
       </c>
       <c r="N208" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B208, $C$2:$C$820, C208, $D$2:$D$820, D208, $E$2:$E$820, E208) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O208" s="12"/>
@@ -10246,7 +10200,7 @@
         <v>501</v>
       </c>
       <c r="N209" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B209, $C$2:$C$820, C209, $D$2:$D$820, D209, $E$2:$E$820, E209) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10282,7 +10236,7 @@
         <v>118</v>
       </c>
       <c r="N210" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B210, $C$2:$C$820, C210, $D$2:$D$820, D210, $E$2:$E$820, E210) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O210" s="12"/>
@@ -10319,11 +10273,11 @@
         <v>55</v>
       </c>
       <c r="N211" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B211, $C$2:$C$820, C211, $D$2:$D$820, D211, $E$2:$E$820, E211) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="212" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="212" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A212" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -10365,7 +10319,7 @@
         <v>275</v>
       </c>
       <c r="N212" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B212, $C$2:$C$820, C212, $D$2:$D$820, D212, $E$2:$E$820, E212) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10401,7 +10355,7 @@
         <v>118</v>
       </c>
       <c r="N213" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B213, $C$2:$C$820, C213, $D$2:$D$820, D213, $E$2:$E$820, E213) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O213" s="12"/>
@@ -10438,7 +10392,7 @@
         <v>117</v>
       </c>
       <c r="N214" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B214, $C$2:$C$820, C214, $D$2:$D$820, D214, $E$2:$E$820, E214) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O214" s="12"/>
@@ -10476,7 +10430,7 @@
       <c r="L215" s="20"/>
       <c r="M215" s="20"/>
       <c r="N215" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B215, $C$2:$C$820, C215, $D$2:$D$820, D215, $E$2:$E$820, E215) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O215" s="12"/>
@@ -10513,57 +10467,56 @@
         <v>118</v>
       </c>
       <c r="N216" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B216, $C$2:$C$820, C216, $D$2:$D$820, D216, $E$2:$E$820, E216) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O216" s="12"/>
     </row>
-    <row r="217" spans="1:15" s="76" customFormat="1" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A217" s="77">
+    <row r="217" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A217" s="3">
         <v>46260.425694444442</v>
       </c>
-      <c r="B217" s="73" t="s">
+      <c r="B217" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C217" s="73" t="s">
-        <v>7</v>
-      </c>
-      <c r="D217" s="70">
+      <c r="C217" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D217" s="4">
         <v>20</v>
       </c>
-      <c r="E217" s="70">
+      <c r="E217" s="4">
         <v>1924</v>
       </c>
-      <c r="F217" s="70">
+      <c r="F217" s="4">
         <v>10.638297870000001</v>
       </c>
-      <c r="G217" s="71" t="s">
+      <c r="G217" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="H217" s="72">
+      <c r="H217" s="5">
         <v>1739</v>
       </c>
-      <c r="I217" s="73" t="s">
-        <v>8</v>
-      </c>
-      <c r="J217" s="75" t="s">
+      <c r="I217" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J217" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="K217" s="75" t="s">
+      <c r="K217" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="L217" s="75">
+      <c r="L217" s="20">
         <v>37480</v>
       </c>
-      <c r="M217" s="75">
+      <c r="M217" s="20">
         <f>ABS((D217*E217)-L217)</f>
         <v>1000</v>
       </c>
-      <c r="N217" s="78" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B217, $C$2:$C$820, C217, $D$2:$D$820, D217, $E$2:$E$820, E217) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O217" s="75"/>
+      <c r="N217" t="str">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
     </row>
     <row r="218" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A218" s="10" t="s">
@@ -10595,7 +10548,7 @@
       </c>
       <c r="J218" s="54"/>
       <c r="N218" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B218, $C$2:$C$820, C218, $D$2:$D$820, D218, $E$2:$E$820, E218) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O218" s="12"/>
@@ -10642,7 +10595,7 @@
         <v>300</v>
       </c>
       <c r="N219" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B219, $C$2:$C$820, C219, $D$2:$D$820, D219, $E$2:$E$820, E219) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10688,7 +10641,7 @@
         <v>300</v>
       </c>
       <c r="N220" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B220, $C$2:$C$820, C220, $D$2:$D$820, D220, $E$2:$E$820, E220) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10724,7 +10677,7 @@
         <v>118</v>
       </c>
       <c r="N221" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B221, $C$2:$C$820, C221, $D$2:$D$820, D221, $E$2:$E$820, E221) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O221" s="12"/>
@@ -10771,11 +10724,11 @@
         <v>500</v>
       </c>
       <c r="N222" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B222, $C$2:$C$820, C222, $D$2:$D$820, D222, $E$2:$E$820, E222) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="223" spans="1:15" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="7"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="223" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A223" s="3">
         <v>46260.557638888888</v>
       </c>
@@ -10817,7 +10770,7 @@
         <v>250</v>
       </c>
       <c r="N223" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B223, $C$2:$C$820, C223, $D$2:$D$820, D223, $E$2:$E$820, E223) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10851,7 +10804,7 @@
       </c>
       <c r="J224" s="54"/>
       <c r="N224" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B224, $C$2:$C$820, C224, $D$2:$D$820, D224, $E$2:$E$820, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O224" s="12"/>
@@ -10898,7 +10851,7 @@
         <v>300</v>
       </c>
       <c r="N225" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B225, $C$2:$C$820, C225, $D$2:$D$820, D225, $E$2:$E$820, E225) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10944,7 +10897,7 @@
         <v>188</v>
       </c>
       <c r="N226" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B226, $C$2:$C$820, C226, $D$2:$D$820, D226, $E$2:$E$820, E226) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10990,7 +10943,7 @@
         <v>140</v>
       </c>
       <c r="N227" s="49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B227, $C$2:$C$820, C227, $D$2:$D$820, D227, $E$2:$E$820, E227) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
       <c r="O227" s="47"/>
@@ -11037,7 +10990,7 @@
         <v>300</v>
       </c>
       <c r="N228" s="49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B228, $C$2:$C$820, C228, $D$2:$D$820, D228, $E$2:$E$820, E228) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Duplicate</v>
       </c>
       <c r="O228" s="47"/>
@@ -11074,7 +11027,7 @@
         <v>118</v>
       </c>
       <c r="N229" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B229, $C$2:$C$820, C229, $D$2:$D$820, D229, $E$2:$E$820, E229) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O229" s="12"/>
@@ -11114,7 +11067,7 @@
         <v>144</v>
       </c>
       <c r="N230" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B230, $C$2:$C$820, C230, $D$2:$D$820, D230, $E$2:$E$820, E230) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O230" s="12"/>
@@ -11161,7 +11114,7 @@
         <v>940</v>
       </c>
       <c r="N231" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B231, $C$2:$C$820, C231, $D$2:$D$820, D231, $E$2:$E$820, E231) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11197,7 +11150,7 @@
         <v>117</v>
       </c>
       <c r="N232" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B232, $C$2:$C$820, C232, $D$2:$D$820, D232, $E$2:$E$820, E232) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O232" s="12"/>
@@ -11244,7 +11197,7 @@
         <v>500</v>
       </c>
       <c r="N233" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B233, $C$2:$C$820, C233, $D$2:$D$820, D233, $E$2:$E$820, E233) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11280,7 +11233,7 @@
         <v>117</v>
       </c>
       <c r="N234" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B234, $C$2:$C$820, C234, $D$2:$D$820, D234, $E$2:$E$820, E234) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11326,7 +11279,7 @@
         <v>300</v>
       </c>
       <c r="N235" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B235, $C$2:$C$820, C235, $D$2:$D$820, D235, $E$2:$E$820, E235) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11365,7 +11318,7 @@
       <c r="L236" s="20"/>
       <c r="M236" s="20"/>
       <c r="N236" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B236, $C$2:$C$820, C236, $D$2:$D$820, D236, $E$2:$E$820, E236) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O236" s="20"/>
@@ -11400,7 +11353,7 @@
       </c>
       <c r="J237" s="54"/>
       <c r="N237" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B237, $C$2:$C$820, C237, $D$2:$D$820, D237, $E$2:$E$820, E237) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O237" s="12"/>
@@ -11437,7 +11390,7 @@
         <v>118</v>
       </c>
       <c r="N238" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B238, $C$2:$C$820, C238, $D$2:$D$820, D238, $E$2:$E$820, E238) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O238" s="12"/>
@@ -11474,7 +11427,7 @@
         <v>118</v>
       </c>
       <c r="N239" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B239, $C$2:$C$820, C239, $D$2:$D$820, D239, $E$2:$E$820, E239) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O239" s="12"/>
@@ -11509,7 +11462,7 @@
       </c>
       <c r="J240" s="54"/>
       <c r="N240" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B240, $C$2:$C$820, C240, $D$2:$D$820, D240, $E$2:$E$820, E240) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O240" s="12"/>
@@ -11544,7 +11497,7 @@
       </c>
       <c r="J241" s="54"/>
       <c r="N241" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B241, $C$2:$C$820, C241, $D$2:$D$820, D241, $E$2:$E$820, E241) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O241" s="12"/>
@@ -11579,7 +11532,7 @@
       </c>
       <c r="J242" s="54"/>
       <c r="N242" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B242, $C$2:$C$820, C242, $D$2:$D$820, D242, $E$2:$E$820, E242) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O242" s="12"/>
@@ -11626,7 +11579,7 @@
         <v>650</v>
       </c>
       <c r="N243" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B243, $C$2:$C$820, C243, $D$2:$D$820, D243, $E$2:$E$820, E243) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11663,7 +11616,7 @@
       <c r="L244" s="20"/>
       <c r="M244" s="20"/>
       <c r="N244" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B244, $C$2:$C$820, C244, $D$2:$D$820, D244, $E$2:$E$820, E244) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O244" s="12"/>
@@ -11698,7 +11651,7 @@
       </c>
       <c r="J245" s="54"/>
       <c r="N245" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B245, $C$2:$C$820, C245, $D$2:$D$820, D245, $E$2:$E$820, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O245" s="12"/>
@@ -11733,7 +11686,7 @@
       </c>
       <c r="J246" s="54"/>
       <c r="N246" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B246, $C$2:$C$820, C246, $D$2:$D$820, D246, $E$2:$E$820, E246) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O246" s="12"/>
@@ -11768,7 +11721,7 @@
       </c>
       <c r="J247" s="54"/>
       <c r="N247" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B247, $C$2:$C$820, C247, $D$2:$D$820, D247, $E$2:$E$820, E247) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O247" s="12"/>
@@ -11808,7 +11761,7 @@
         <v>146</v>
       </c>
       <c r="N248" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B248, $C$2:$C$820, C248, $D$2:$D$820, D248, $E$2:$E$820, E248) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11854,7 +11807,7 @@
         <v>480</v>
       </c>
       <c r="N249" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B249, $C$2:$C$820, C249, $D$2:$D$820, D249, $E$2:$E$820, E249) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O249" s="20"/>
@@ -11894,7 +11847,7 @@
       <c r="L250" s="20"/>
       <c r="M250" s="20"/>
       <c r="N250" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B250, $C$2:$C$820, C250, $D$2:$D$820, D250, $E$2:$E$820, E250) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O250" s="12"/>
@@ -11929,7 +11882,7 @@
       </c>
       <c r="J251" s="54"/>
       <c r="N251" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B251, $C$2:$C$820, C251, $D$2:$D$820, D251, $E$2:$E$820, E251) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O251" s="12"/>
@@ -11964,7 +11917,7 @@
       </c>
       <c r="J252" s="54"/>
       <c r="N252" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B252, $C$2:$C$820, C252, $D$2:$D$820, D252, $E$2:$E$820, E252) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11996,9 +11949,9 @@
       <c r="I253" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J253" s="60"/>
+      <c r="J253" s="54"/>
       <c r="N253" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B253, $C$2:$C$820, C253, $D$2:$D$820, D253, $E$2:$E$820, E253) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12032,7 +11985,7 @@
       </c>
       <c r="J254" s="54"/>
       <c r="N254" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B254, $C$2:$C$820, C254, $D$2:$D$820, D254, $E$2:$E$820, E254) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O254" s="12"/>
@@ -12069,7 +12022,7 @@
         <v>118</v>
       </c>
       <c r="N255" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B255, $C$2:$C$820, C255, $D$2:$D$820, D255, $E$2:$E$820, E255) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O255" s="12"/>
@@ -12104,7 +12057,7 @@
       </c>
       <c r="J256" s="54"/>
       <c r="N256" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B256, $C$2:$C$820, C256, $D$2:$D$820, D256, $E$2:$E$820, E256) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O256" s="12"/>
@@ -12141,7 +12094,7 @@
         <v>118</v>
       </c>
       <c r="N257" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B257, $C$2:$C$820, C257, $D$2:$D$820, D257, $E$2:$E$820, E257) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O257" s="12"/>
@@ -12176,7 +12129,7 @@
       </c>
       <c r="J258" s="54"/>
       <c r="N258" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B258, $C$2:$C$820, C258, $D$2:$D$820, D258, $E$2:$E$820, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N258:N280" si="8">IF(COUNTIFS( $B$2:$B$820, B258, $C$2:$C$820, C258, $D$2:$D$820, D258, $E$2:$E$820, E258) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -12210,7 +12163,7 @@
       </c>
       <c r="J259" s="54"/>
       <c r="N259" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B259, $C$2:$C$820, C259, $D$2:$D$820, D259, $E$2:$E$820, E259) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O259" s="12"/>
@@ -12245,7 +12198,7 @@
       </c>
       <c r="J260" s="54"/>
       <c r="N260" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B260, $C$2:$C$820, C260, $D$2:$D$820, D260, $E$2:$E$820, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O260" s="19"/>
@@ -12280,7 +12233,7 @@
       </c>
       <c r="J261" s="54"/>
       <c r="N261" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B261, $C$2:$C$820, C261, $D$2:$D$820, D261, $E$2:$E$820, E261) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O261" s="12"/>
@@ -12327,7 +12280,7 @@
         <v>250</v>
       </c>
       <c r="N262" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B262, $C$2:$C$820, C262, $D$2:$D$820, D262, $E$2:$E$820, E262) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12361,7 +12314,7 @@
       </c>
       <c r="J263" s="54"/>
       <c r="N263" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B263, $C$2:$C$820, C263, $D$2:$D$820, D263, $E$2:$E$820, E263) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12397,7 +12350,7 @@
         <v>55</v>
       </c>
       <c r="N264" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B264, $C$2:$C$820, C264, $D$2:$D$820, D264, $E$2:$E$820, E264) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O264" s="12"/>
@@ -12434,7 +12387,7 @@
         <v>117</v>
       </c>
       <c r="N265" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B265, $C$2:$C$820, C265, $D$2:$D$820, D265, $E$2:$E$820, E265) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O265" s="12"/>
@@ -12471,7 +12424,7 @@
         <v>118</v>
       </c>
       <c r="N266" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B266, $C$2:$C$820, C266, $D$2:$D$820, D266, $E$2:$E$820, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12505,7 +12458,7 @@
       </c>
       <c r="J267" s="54"/>
       <c r="N267" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B267, $C$2:$C$820, C267, $D$2:$D$820, D267, $E$2:$E$820, E267) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O267" s="19"/>
@@ -12552,7 +12505,7 @@
         <v>300</v>
       </c>
       <c r="N268" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B268, $C$2:$C$820, C268, $D$2:$D$820, D268, $E$2:$E$820, E268) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12586,7 +12539,7 @@
       </c>
       <c r="J269" s="54"/>
       <c r="N269" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B269, $C$2:$C$820, C269, $D$2:$D$820, D269, $E$2:$E$820, E269) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O269" s="12"/>
@@ -12623,7 +12576,7 @@
         <v>118</v>
       </c>
       <c r="N270" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B270, $C$2:$C$820, C270, $D$2:$D$820, D270, $E$2:$E$820, E270) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O270" s="19"/>
@@ -12660,7 +12613,7 @@
         <v>118</v>
       </c>
       <c r="N271" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B271, $C$2:$C$820, C271, $D$2:$D$820, D271, $E$2:$E$820, E271) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12697,7 +12650,7 @@
       <c r="L272" s="20"/>
       <c r="M272" s="20"/>
       <c r="N272" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B272, $C$2:$C$820, C272, $D$2:$D$820, D272, $E$2:$E$820, E272) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O272" s="12"/>
@@ -12732,7 +12685,7 @@
       </c>
       <c r="J273" s="54"/>
       <c r="N273" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B273, $C$2:$C$820, C273, $D$2:$D$820, D273, $E$2:$E$820, E273) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12768,7 +12721,7 @@
         <v>118</v>
       </c>
       <c r="N274" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B274, $C$2:$C$820, C274, $D$2:$D$820, D274, $E$2:$E$820, E274) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O274" s="19"/>
@@ -12803,7 +12756,7 @@
       </c>
       <c r="J275" s="54"/>
       <c r="N275" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B275, $C$2:$C$820, C275, $D$2:$D$820, D275, $E$2:$E$820, E275) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O275" s="19"/>
@@ -12850,7 +12803,7 @@
         <v>250</v>
       </c>
       <c r="N276" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B276, $C$2:$C$820, C276, $D$2:$D$820, D276, $E$2:$E$820, E276) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12887,7 +12840,7 @@
       <c r="L277" s="20"/>
       <c r="M277" s="20"/>
       <c r="N277" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B277, $C$2:$C$820, C277, $D$2:$D$820, D277, $E$2:$E$820, E277) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O277" s="19"/>
@@ -12922,7 +12875,7 @@
       </c>
       <c r="J278" s="54"/>
       <c r="N278" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B278, $C$2:$C$820, C278, $D$2:$D$820, D278, $E$2:$E$820, E278) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O278" s="19"/>
@@ -12957,7 +12910,7 @@
       </c>
       <c r="J279" s="54"/>
       <c r="N279" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B279, $C$2:$C$820, C279, $D$2:$D$820, D279, $E$2:$E$820, E279) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O279" s="19"/>
@@ -12992,7 +12945,7 @@
       </c>
       <c r="J280" s="54"/>
       <c r="N280" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$820, B280, $C$2:$C$820, C280, $D$2:$D$820, D280, $E$2:$E$820, E280) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O280" s="19"/>
@@ -13002,9 +12955,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:O280" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
+    <filterColumn colId="1">
       <filters>
-        <filter val="B"/>
+        <filter val="ARE&amp;MEQ"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O101">
@@ -13074,7 +13027,7 @@
         <v>4120</v>
       </c>
       <c r="L2" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$908, B2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="L2:L19" si="0">IF(COUNTIFS( $B$2:$B$908, B2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -13098,15 +13051,15 @@
         <v>30</v>
       </c>
       <c r="I3" t="str">
-        <f t="shared" ref="I3" si="0">C3 &amp; " " &amp; D3 &amp; "*" &amp; E3 &amp; " :" &amp; A3</f>
+        <f t="shared" ref="I3" si="1">C3 &amp; " " &amp; D3 &amp; "*" &amp; E3 &amp; " :" &amp; A3</f>
         <v>B 100*329 :02 SEP 2026 11:04:43 AM</v>
       </c>
       <c r="J3">
-        <f t="shared" ref="J3" si="1">D3*E3</f>
+        <f t="shared" ref="J3" si="2">D3*E3</f>
         <v>32900</v>
       </c>
       <c r="L3" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$908, B3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -13134,11 +13087,11 @@
         <v>B 2*2484 :02 SEP 2026 10:11:18 AM</v>
       </c>
       <c r="J4">
-        <f t="shared" ref="J4:J6" si="2">D4*E4</f>
+        <f t="shared" ref="J4:J6" si="3">D4*E4</f>
         <v>4968</v>
       </c>
       <c r="L4" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$908, B4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13162,15 +13115,15 @@
         <v>30</v>
       </c>
       <c r="I5" t="str">
-        <f t="shared" ref="I5:I6" si="3">C5 &amp; " " &amp; D5 &amp; "*" &amp; E5 &amp; " :" &amp; A5</f>
+        <f t="shared" ref="I5:I6" si="4">C5 &amp; " " &amp; D5 &amp; "*" &amp; E5 &amp; " :" &amp; A5</f>
         <v>B 10*601 :02 SEP 2026 09:00:47 AM</v>
       </c>
       <c r="J5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6010</v>
       </c>
       <c r="L5" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$908, B5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13194,15 +13147,15 @@
         <v>30</v>
       </c>
       <c r="I6" t="str">
+        <f t="shared" si="4"/>
+        <v>B 100*332 :02 SEP 2026 09:21:33 AM</v>
+      </c>
+      <c r="J6">
         <f t="shared" si="3"/>
-        <v>B 100*332 :02 SEP 2026 09:21:33 AM</v>
-      </c>
-      <c r="J6">
-        <f t="shared" si="2"/>
         <v>33200</v>
       </c>
       <c r="L6" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$908, B6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -13226,15 +13179,15 @@
         <v>30</v>
       </c>
       <c r="I7" t="str">
-        <f t="shared" ref="I7:I19" si="4">C7 &amp; " " &amp; D7 &amp; "*" &amp; E7 &amp; " :" &amp; A7</f>
+        <f t="shared" ref="I7:I19" si="5">C7 &amp; " " &amp; D7 &amp; "*" &amp; E7 &amp; " :" &amp; A7</f>
         <v>B 20*917 :02 SEP 2026 09:00:50 AM</v>
       </c>
       <c r="J7">
-        <f t="shared" ref="J7:J19" si="5">D7*E7</f>
+        <f t="shared" ref="J7:J19" si="6">D7*E7</f>
         <v>18340</v>
       </c>
       <c r="L7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$908, B7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -13258,15 +13211,15 @@
         <v>30</v>
       </c>
       <c r="I8" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>B 3*1360 :02 SEP 2026 09:00:50 AM</v>
       </c>
       <c r="J8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4080</v>
       </c>
       <c r="L8" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$908, B8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13290,15 +13243,15 @@
         <v>30</v>
       </c>
       <c r="I9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>B 2*4110 :02 SEP 2026 09:00:50 AM</v>
       </c>
       <c r="J9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8220</v>
       </c>
       <c r="L9" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$908, B9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13322,15 +13275,15 @@
         <v>30</v>
       </c>
       <c r="I10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>B 20*870 :02 SEP 2026 09:00:50 AM</v>
       </c>
       <c r="J10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>17400</v>
       </c>
       <c r="L10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$908, B10) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13354,15 +13307,15 @@
         <v>30</v>
       </c>
       <c r="I11" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>B 5*1151 :02 SEP 2026 09:00:50 AM</v>
       </c>
       <c r="J11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5755</v>
       </c>
       <c r="L11" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$908, B11) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -13386,15 +13339,15 @@
         <v>30</v>
       </c>
       <c r="I12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>B 150*215 :02 SEP 2026 10:17:03 AM</v>
       </c>
       <c r="J12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>32250</v>
       </c>
       <c r="L12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$908, B12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13418,15 +13371,15 @@
         <v>30</v>
       </c>
       <c r="I13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>B 5*2496 :02 SEP 2026 12:20:03 PM</v>
       </c>
       <c r="J13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>12480</v>
       </c>
       <c r="L13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$908, B13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13450,15 +13403,15 @@
         <v>30</v>
       </c>
       <c r="I14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>B 50*335.1 :02 SEP 2026 09:00:47 AM</v>
       </c>
       <c r="J14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>16755</v>
       </c>
       <c r="L14" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$908, B14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -13482,15 +13435,15 @@
         <v>30</v>
       </c>
       <c r="I15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>B 10*927 :02 SEP 2026 09:00:50 AM</v>
       </c>
       <c r="J15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9270</v>
       </c>
       <c r="L15" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$908, B15) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -13514,15 +13467,15 @@
         <v>30</v>
       </c>
       <c r="I16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>B 5*1161 :02 SEP 2026 09:00:47 AM</v>
       </c>
       <c r="J16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5805</v>
       </c>
       <c r="L16" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$908, B16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -13546,15 +13499,15 @@
         <v>30</v>
       </c>
       <c r="I17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>B 25*345 :02 SEP 2026 09:57:46 AM</v>
       </c>
       <c r="J17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8625</v>
       </c>
       <c r="L17" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$908, B17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13578,15 +13531,15 @@
         <v>30</v>
       </c>
       <c r="I18" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>B 2*3210 :02 SEP 2026 09:00:50 AM</v>
       </c>
       <c r="J18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>6420</v>
       </c>
       <c r="L18" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$908, B18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13610,15 +13563,15 @@
         <v>30</v>
       </c>
       <c r="I19" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>S 1*20350 :02 SEP 2026 09:00:38 AM</v>
       </c>
       <c r="J19">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>20350</v>
       </c>
       <c r="L19" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$908, B19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13725,7 +13678,7 @@
       <c r="L2" s="19"/>
       <c r="M2" s="19"/>
       <c r="N2" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B2, $C$2:$C$824, C2, $D$2:$D$824, D2, $E$2:$E$824, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N65" si="0">IF(COUNTIFS( $B$2:$B$824, B2, $C$2:$C$824, C2, $D$2:$D$824, D2, $E$2:$E$824, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O2" s="19"/>
@@ -13772,7 +13725,7 @@
         <v>580</v>
       </c>
       <c r="N3" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B3, $C$2:$C$824, C3, $D$2:$D$824, D3, $E$2:$E$824, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O3" s="20"/>
@@ -13810,7 +13763,7 @@
       <c r="L4" s="19"/>
       <c r="M4" s="19"/>
       <c r="N4" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B4, $C$2:$C$824, C4, $D$2:$D$824, D4, $E$2:$E$824, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O4" s="19"/>
@@ -13848,7 +13801,7 @@
       <c r="L5" s="19"/>
       <c r="M5" s="19"/>
       <c r="N5" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B5, $C$2:$C$824, C5, $D$2:$D$824, D5, $E$2:$E$824, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O5" s="19"/>
@@ -13895,7 +13848,7 @@
         <v>442</v>
       </c>
       <c r="N6" s="42" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B6, $C$2:$C$824, C6, $D$2:$D$824, D6, $E$2:$E$824, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O6" s="41"/>
@@ -13935,7 +13888,7 @@
       <c r="L7" s="19"/>
       <c r="M7" s="19"/>
       <c r="N7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B7, $C$2:$C$824, C7, $D$2:$D$824, D7, $E$2:$E$824, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O7" s="19"/>
@@ -13982,7 +13935,7 @@
         <v>320</v>
       </c>
       <c r="N8" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B8, $C$2:$C$824, C8, $D$2:$D$824, D8, $E$2:$E$824, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O8" s="20"/>
@@ -14020,7 +13973,7 @@
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
       <c r="N9" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B9, $C$2:$C$824, C9, $D$2:$D$824, D9, $E$2:$E$824, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O9" s="19"/>
@@ -14067,7 +14020,7 @@
         <v>300</v>
       </c>
       <c r="N10" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B10, $C$2:$C$824, C10, $D$2:$D$824, D10, $E$2:$E$824, E10) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O10" s="20"/>
@@ -14107,7 +14060,7 @@
       <c r="L11" s="19"/>
       <c r="M11" s="19"/>
       <c r="N11" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B11, $C$2:$C$824, C11, $D$2:$D$824, D11, $E$2:$E$824, E11) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O11" s="19"/>
@@ -14145,7 +14098,7 @@
       <c r="L12" s="19"/>
       <c r="M12" s="19"/>
       <c r="N12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B12, $C$2:$C$824, C12, $D$2:$D$824, D12, $E$2:$E$824, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O12" s="19"/>
@@ -14183,7 +14136,7 @@
       <c r="L13" s="19"/>
       <c r="M13" s="19"/>
       <c r="N13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B13, $C$2:$C$824, C13, $D$2:$D$824, D13, $E$2:$E$824, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O13" s="19"/>
@@ -14221,7 +14174,7 @@
       <c r="L14" s="19"/>
       <c r="M14" s="19"/>
       <c r="N14" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B14, $C$2:$C$824, C14, $D$2:$D$824, D14, $E$2:$E$824, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O14" s="19"/>
@@ -14261,7 +14214,7 @@
       <c r="L15" s="19"/>
       <c r="M15" s="19"/>
       <c r="N15" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B15, $C$2:$C$824, C15, $D$2:$D$824, D15, $E$2:$E$824, E15) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O15" s="19"/>
@@ -14301,7 +14254,7 @@
       <c r="L16" s="19"/>
       <c r="M16" s="19"/>
       <c r="N16" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B16, $C$2:$C$824, C16, $D$2:$D$824, D16, $E$2:$E$824, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O16" s="19"/>
@@ -14341,7 +14294,7 @@
       <c r="L17" s="19"/>
       <c r="M17" s="19"/>
       <c r="N17" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B17, $C$2:$C$824, C17, $D$2:$D$824, D17, $E$2:$E$824, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O17" s="19"/>
@@ -14379,7 +14332,7 @@
       <c r="L18" s="19"/>
       <c r="M18" s="19"/>
       <c r="N18" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B18, $C$2:$C$824, C18, $D$2:$D$824, D18, $E$2:$E$824, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O18" s="19"/>
@@ -14419,7 +14372,7 @@
       <c r="L19" s="19"/>
       <c r="M19" s="19"/>
       <c r="N19" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B19, $C$2:$C$824, C19, $D$2:$D$824, D19, $E$2:$E$824, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O19" s="19"/>
@@ -14457,7 +14410,7 @@
       <c r="L20" s="19"/>
       <c r="M20" s="19"/>
       <c r="N20" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B20, $C$2:$C$824, C20, $D$2:$D$824, D20, $E$2:$E$824, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O20" s="19"/>
@@ -14495,7 +14448,7 @@
       <c r="L21" s="19"/>
       <c r="M21" s="19"/>
       <c r="N21" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B21, $C$2:$C$824, C21, $D$2:$D$824, D21, $E$2:$E$824, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O21" s="19"/>
@@ -14533,7 +14486,7 @@
       <c r="L22" s="19"/>
       <c r="M22" s="19"/>
       <c r="N22" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B22, $C$2:$C$824, C22, $D$2:$D$824, D22, $E$2:$E$824, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O22" s="19"/>
@@ -14571,7 +14524,7 @@
       <c r="L23" s="19"/>
       <c r="M23" s="19"/>
       <c r="N23" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B23, $C$2:$C$824, C23, $D$2:$D$824, D23, $E$2:$E$824, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O23" s="19"/>
@@ -14611,7 +14564,7 @@
       <c r="L24" s="19"/>
       <c r="M24" s="19"/>
       <c r="N24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B24, $C$2:$C$824, C24, $D$2:$D$824, D24, $E$2:$E$824, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O24" s="19"/>
@@ -14649,7 +14602,7 @@
       <c r="L25" s="19"/>
       <c r="M25" s="19"/>
       <c r="N25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B25, $C$2:$C$824, C25, $D$2:$D$824, D25, $E$2:$E$824, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O25" s="19"/>
@@ -14696,7 +14649,7 @@
         <v>300</v>
       </c>
       <c r="N26" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B26, $C$2:$C$824, C26, $D$2:$D$824, D26, $E$2:$E$824, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O26" s="20"/>
@@ -14734,7 +14687,7 @@
       <c r="L27" s="19"/>
       <c r="M27" s="19"/>
       <c r="N27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B27, $C$2:$C$824, C27, $D$2:$D$824, D27, $E$2:$E$824, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O27" s="19"/>
@@ -14781,7 +14734,7 @@
         <v>250</v>
       </c>
       <c r="N28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B28, $C$2:$C$824, C28, $D$2:$D$824, D28, $E$2:$E$824, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O28" s="20"/>
@@ -14819,7 +14772,7 @@
       <c r="L29" s="19"/>
       <c r="M29" s="19"/>
       <c r="N29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B29, $C$2:$C$824, C29, $D$2:$D$824, D29, $E$2:$E$824, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O29" s="19"/>
@@ -14857,7 +14810,7 @@
       <c r="L30" s="19"/>
       <c r="M30" s="19"/>
       <c r="N30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B30, $C$2:$C$824, C30, $D$2:$D$824, D30, $E$2:$E$824, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O30" s="19"/>
@@ -14895,7 +14848,7 @@
       <c r="L31" s="19"/>
       <c r="M31" s="19"/>
       <c r="N31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B31, $C$2:$C$824, C31, $D$2:$D$824, D31, $E$2:$E$824, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O31" s="19"/>
@@ -14933,7 +14886,7 @@
       <c r="L32" s="19"/>
       <c r="M32" s="19"/>
       <c r="N32" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B32, $C$2:$C$824, C32, $D$2:$D$824, D32, $E$2:$E$824, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O32" s="19"/>
@@ -14973,7 +14926,7 @@
       <c r="L33" s="19"/>
       <c r="M33" s="19"/>
       <c r="N33" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B33, $C$2:$C$824, C33, $D$2:$D$824, D33, $E$2:$E$824, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O33" s="19"/>
@@ -15011,7 +14964,7 @@
       <c r="L34" s="19"/>
       <c r="M34" s="19"/>
       <c r="N34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B34, $C$2:$C$824, C34, $D$2:$D$824, D34, $E$2:$E$824, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O34" s="19"/>
@@ -15049,7 +15002,7 @@
       <c r="L35" s="19"/>
       <c r="M35" s="19"/>
       <c r="N35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B35, $C$2:$C$824, C35, $D$2:$D$824, D35, $E$2:$E$824, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O35" s="19"/>
@@ -15087,7 +15040,7 @@
       <c r="L36" s="19"/>
       <c r="M36" s="19"/>
       <c r="N36" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B36, $C$2:$C$824, C36, $D$2:$D$824, D36, $E$2:$E$824, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O36" s="19"/>
@@ -15127,7 +15080,7 @@
       <c r="L37" s="19"/>
       <c r="M37" s="19"/>
       <c r="N37" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B37, $C$2:$C$824, C37, $D$2:$D$824, D37, $E$2:$E$824, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O37" s="19"/>
@@ -15165,7 +15118,7 @@
       <c r="L38" s="19"/>
       <c r="M38" s="19"/>
       <c r="N38" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B38, $C$2:$C$824, C38, $D$2:$D$824, D38, $E$2:$E$824, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O38" s="19"/>
@@ -15212,7 +15165,7 @@
         <v>400</v>
       </c>
       <c r="N39" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B39, $C$2:$C$824, C39, $D$2:$D$824, D39, $E$2:$E$824, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O39" s="20"/>
@@ -15250,7 +15203,7 @@
       <c r="L40" s="19"/>
       <c r="M40" s="19"/>
       <c r="N40" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B40, $C$2:$C$824, C40, $D$2:$D$824, D40, $E$2:$E$824, E40) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O40" s="19"/>
@@ -15290,7 +15243,7 @@
       <c r="L41" s="19"/>
       <c r="M41" s="19"/>
       <c r="N41" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B41, $C$2:$C$824, C41, $D$2:$D$824, D41, $E$2:$E$824, E41) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O41" s="19"/>
@@ -15337,7 +15290,7 @@
         <v>300</v>
       </c>
       <c r="N42" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B42, $C$2:$C$824, C42, $D$2:$D$824, D42, $E$2:$E$824, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O42" s="20"/>
@@ -15375,7 +15328,7 @@
       <c r="L43" s="19"/>
       <c r="M43" s="19"/>
       <c r="N43" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B43, $C$2:$C$824, C43, $D$2:$D$824, D43, $E$2:$E$824, E43) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O43" s="19"/>
@@ -15413,7 +15366,7 @@
       <c r="L44" s="19"/>
       <c r="M44" s="19"/>
       <c r="N44" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B44, $C$2:$C$824, C44, $D$2:$D$824, D44, $E$2:$E$824, E44) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O44" s="19"/>
@@ -15451,7 +15404,7 @@
       <c r="L45" s="19"/>
       <c r="M45" s="19"/>
       <c r="N45" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B45, $C$2:$C$824, C45, $D$2:$D$824, D45, $E$2:$E$824, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O45" s="19"/>
@@ -15498,7 +15451,7 @@
         <v>300</v>
       </c>
       <c r="N46" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B46, $C$2:$C$824, C46, $D$2:$D$824, D46, $E$2:$E$824, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O46" s="20"/>
@@ -15536,7 +15489,7 @@
       <c r="L47" s="19"/>
       <c r="M47" s="19"/>
       <c r="N47" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B47, $C$2:$C$824, C47, $D$2:$D$824, D47, $E$2:$E$824, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O47" s="19"/>
@@ -15576,7 +15529,7 @@
       <c r="L48" s="19"/>
       <c r="M48" s="19"/>
       <c r="N48" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B48, $C$2:$C$824, C48, $D$2:$D$824, D48, $E$2:$E$824, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O48" s="19"/>
@@ -15614,7 +15567,7 @@
       <c r="L49" s="19"/>
       <c r="M49" s="19"/>
       <c r="N49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B49, $C$2:$C$824, C49, $D$2:$D$824, D49, $E$2:$E$824, E49) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O49" s="19"/>
@@ -15652,7 +15605,7 @@
       <c r="L50" s="19"/>
       <c r="M50" s="19"/>
       <c r="N50" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B50, $C$2:$C$824, C50, $D$2:$D$824, D50, $E$2:$E$824, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O50" s="19"/>
@@ -15690,7 +15643,7 @@
       <c r="L51" s="19"/>
       <c r="M51" s="19"/>
       <c r="N51" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B51, $C$2:$C$824, C51, $D$2:$D$824, D51, $E$2:$E$824, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O51" s="19"/>
@@ -15728,7 +15681,7 @@
       <c r="L52" s="19"/>
       <c r="M52" s="19"/>
       <c r="N52" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B52, $C$2:$C$824, C52, $D$2:$D$824, D52, $E$2:$E$824, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O52" s="19"/>
@@ -15766,7 +15719,7 @@
       <c r="L53" s="19"/>
       <c r="M53" s="19"/>
       <c r="N53" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B53, $C$2:$C$824, C53, $D$2:$D$824, D53, $E$2:$E$824, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O53" s="19"/>
@@ -15806,7 +15759,7 @@
       <c r="L54" s="19"/>
       <c r="M54" s="19"/>
       <c r="N54" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B54, $C$2:$C$824, C54, $D$2:$D$824, D54, $E$2:$E$824, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O54" s="19"/>
@@ -15846,7 +15799,7 @@
       <c r="L55" s="19"/>
       <c r="M55" s="19"/>
       <c r="N55" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B55, $C$2:$C$824, C55, $D$2:$D$824, D55, $E$2:$E$824, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O55" s="19"/>
@@ -15884,7 +15837,7 @@
       <c r="L56" s="19"/>
       <c r="M56" s="19"/>
       <c r="N56" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B56, $C$2:$C$824, C56, $D$2:$D$824, D56, $E$2:$E$824, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O56" s="19"/>
@@ -15924,7 +15877,7 @@
       <c r="L57" s="19"/>
       <c r="M57" s="19"/>
       <c r="N57" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B57, $C$2:$C$824, C57, $D$2:$D$824, D57, $E$2:$E$824, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O57" s="19"/>
@@ -15962,7 +15915,7 @@
       <c r="L58" s="19"/>
       <c r="M58" s="19"/>
       <c r="N58" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B58, $C$2:$C$824, C58, $D$2:$D$824, D58, $E$2:$E$824, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O58" s="19"/>
@@ -16009,7 +15962,7 @@
         <v>222.75</v>
       </c>
       <c r="N59" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B59, $C$2:$C$824, C59, $D$2:$D$824, D59, $E$2:$E$824, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O59" s="20"/>
@@ -16047,7 +16000,7 @@
       <c r="L60" s="19"/>
       <c r="M60" s="19"/>
       <c r="N60" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B60, $C$2:$C$824, C60, $D$2:$D$824, D60, $E$2:$E$824, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O60" s="19"/>
@@ -16087,7 +16040,7 @@
       <c r="L61" s="19"/>
       <c r="M61" s="19"/>
       <c r="N61" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B61, $C$2:$C$824, C61, $D$2:$D$824, D61, $E$2:$E$824, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O61" s="19"/>
@@ -16127,7 +16080,7 @@
       <c r="L62" s="19"/>
       <c r="M62" s="19"/>
       <c r="N62" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B62, $C$2:$C$824, C62, $D$2:$D$824, D62, $E$2:$E$824, E62) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O62" s="19"/>
@@ -16165,7 +16118,7 @@
       <c r="L63" s="19"/>
       <c r="M63" s="19"/>
       <c r="N63" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B63, $C$2:$C$824, C63, $D$2:$D$824, D63, $E$2:$E$824, E63) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O63" s="19"/>
@@ -16203,7 +16156,7 @@
       <c r="L64" s="19"/>
       <c r="M64" s="19"/>
       <c r="N64" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B64, $C$2:$C$824, C64, $D$2:$D$824, D64, $E$2:$E$824, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O64" s="19"/>
@@ -16243,7 +16196,7 @@
       <c r="L65" s="19"/>
       <c r="M65" s="19"/>
       <c r="N65" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B65, $C$2:$C$824, C65, $D$2:$D$824, D65, $E$2:$E$824, E65) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O65" s="19"/>
@@ -16281,7 +16234,7 @@
       <c r="L66" s="19"/>
       <c r="M66" s="19"/>
       <c r="N66" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B66, $C$2:$C$824, C66, $D$2:$D$824, D66, $E$2:$E$824, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N66:N129" si="1">IF(COUNTIFS( $B$2:$B$824, B66, $C$2:$C$824, C66, $D$2:$D$824, D66, $E$2:$E$824, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O66" s="19"/>
@@ -16321,7 +16274,7 @@
       <c r="L67" s="19"/>
       <c r="M67" s="19"/>
       <c r="N67" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B67, $C$2:$C$824, C67, $D$2:$D$824, D67, $E$2:$E$824, E67) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O67" s="19"/>
@@ -16359,7 +16312,7 @@
       <c r="L68" s="19"/>
       <c r="M68" s="19"/>
       <c r="N68" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B68, $C$2:$C$824, C68, $D$2:$D$824, D68, $E$2:$E$824, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O68" s="19"/>
@@ -16397,7 +16350,7 @@
       <c r="L69" s="19"/>
       <c r="M69" s="19"/>
       <c r="N69" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B69, $C$2:$C$824, C69, $D$2:$D$824, D69, $E$2:$E$824, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O69" s="19"/>
@@ -16435,7 +16388,7 @@
       <c r="L70" s="19"/>
       <c r="M70" s="19"/>
       <c r="N70" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B70, $C$2:$C$824, C70, $D$2:$D$824, D70, $E$2:$E$824, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O70" s="19"/>
@@ -16482,7 +16435,7 @@
         <v>300</v>
       </c>
       <c r="N71" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B71, $C$2:$C$824, C71, $D$2:$D$824, D71, $E$2:$E$824, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -16519,7 +16472,7 @@
       <c r="L72" s="19"/>
       <c r="M72" s="19"/>
       <c r="N72" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B72, $C$2:$C$824, C72, $D$2:$D$824, D72, $E$2:$E$824, E72) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O72" s="19"/>
@@ -16557,7 +16510,7 @@
       <c r="L73" s="19"/>
       <c r="M73" s="19"/>
       <c r="N73" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B73, $C$2:$C$824, C73, $D$2:$D$824, D73, $E$2:$E$824, E73) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O73" s="19"/>
@@ -16595,7 +16548,7 @@
       <c r="L74" s="19"/>
       <c r="M74" s="19"/>
       <c r="N74" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B74, $C$2:$C$824, C74, $D$2:$D$824, D74, $E$2:$E$824, E74) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O74" s="19"/>
@@ -16633,7 +16586,7 @@
       <c r="L75" s="19"/>
       <c r="M75" s="19"/>
       <c r="N75" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B75, $C$2:$C$824, C75, $D$2:$D$824, D75, $E$2:$E$824, E75) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O75" s="19"/>
@@ -16673,7 +16626,7 @@
       <c r="L76" s="19"/>
       <c r="M76" s="19"/>
       <c r="N76" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B76, $C$2:$C$824, C76, $D$2:$D$824, D76, $E$2:$E$824, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O76" s="19"/>
@@ -16711,7 +16664,7 @@
       <c r="L77" s="19"/>
       <c r="M77" s="19"/>
       <c r="N77" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B77, $C$2:$C$824, C77, $D$2:$D$824, D77, $E$2:$E$824, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O77" s="19"/>
@@ -16751,7 +16704,7 @@
       <c r="L78" s="19"/>
       <c r="M78" s="19"/>
       <c r="N78" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B78, $C$2:$C$824, C78, $D$2:$D$824, D78, $E$2:$E$824, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O78" s="19"/>
@@ -16789,7 +16742,7 @@
       <c r="L79" s="19"/>
       <c r="M79" s="19"/>
       <c r="N79" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B79, $C$2:$C$824, C79, $D$2:$D$824, D79, $E$2:$E$824, E79) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O79" s="19"/>
@@ -16827,7 +16780,7 @@
       <c r="L80" s="19"/>
       <c r="M80" s="19"/>
       <c r="N80" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B80, $C$2:$C$824, C80, $D$2:$D$824, D80, $E$2:$E$824, E80) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O80" s="19"/>
@@ -16865,7 +16818,7 @@
       <c r="L81" s="19"/>
       <c r="M81" s="19"/>
       <c r="N81" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B81, $C$2:$C$824, C81, $D$2:$D$824, D81, $E$2:$E$824, E81) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O81" s="19"/>
@@ -16907,7 +16860,7 @@
       <c r="L82" s="19"/>
       <c r="M82" s="19"/>
       <c r="N82" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B82, $C$2:$C$824, C82, $D$2:$D$824, D82, $E$2:$E$824, E82) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O82" s="19"/>
@@ -16947,7 +16900,7 @@
       <c r="L83" s="19"/>
       <c r="M83" s="19"/>
       <c r="N83" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B83, $C$2:$C$824, C83, $D$2:$D$824, D83, $E$2:$E$824, E83) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O83" s="19"/>
@@ -16987,7 +16940,7 @@
       <c r="L84" s="19"/>
       <c r="M84" s="19"/>
       <c r="N84" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B84, $C$2:$C$824, C84, $D$2:$D$824, D84, $E$2:$E$824, E84) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O84" s="19"/>
@@ -17025,7 +16978,7 @@
       <c r="L85" s="19"/>
       <c r="M85" s="19"/>
       <c r="N85" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B85, $C$2:$C$824, C85, $D$2:$D$824, D85, $E$2:$E$824, E85) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O85" s="19"/>
@@ -17063,7 +17016,7 @@
       <c r="L86" s="19"/>
       <c r="M86" s="19"/>
       <c r="N86" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B86, $C$2:$C$824, C86, $D$2:$D$824, D86, $E$2:$E$824, E86) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O86" s="19"/>
@@ -17101,7 +17054,7 @@
       <c r="L87" s="19"/>
       <c r="M87" s="19"/>
       <c r="N87" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B87, $C$2:$C$824, C87, $D$2:$D$824, D87, $E$2:$E$824, E87) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O87" s="19"/>
@@ -17139,7 +17092,7 @@
       <c r="L88" s="19"/>
       <c r="M88" s="19"/>
       <c r="N88" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B88, $C$2:$C$824, C88, $D$2:$D$824, D88, $E$2:$E$824, E88) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O88" s="19"/>
@@ -17177,7 +17130,7 @@
       <c r="L89" s="19"/>
       <c r="M89" s="19"/>
       <c r="N89" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B89, $C$2:$C$824, C89, $D$2:$D$824, D89, $E$2:$E$824, E89) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O89" s="19"/>
@@ -17215,7 +17168,7 @@
       <c r="L90" s="19"/>
       <c r="M90" s="19"/>
       <c r="N90" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B90, $C$2:$C$824, C90, $D$2:$D$824, D90, $E$2:$E$824, E90) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O90" s="19"/>
@@ -17255,7 +17208,7 @@
       <c r="L91" s="19"/>
       <c r="M91" s="19"/>
       <c r="N91" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B91, $C$2:$C$824, C91, $D$2:$D$824, D91, $E$2:$E$824, E91) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O91" s="19"/>
@@ -17293,7 +17246,7 @@
       <c r="L92" s="19"/>
       <c r="M92" s="19"/>
       <c r="N92" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B92, $C$2:$C$824, C92, $D$2:$D$824, D92, $E$2:$E$824, E92) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O92" s="19"/>
@@ -17331,7 +17284,7 @@
       <c r="L93" s="19"/>
       <c r="M93" s="19"/>
       <c r="N93" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B93, $C$2:$C$824, C93, $D$2:$D$824, D93, $E$2:$E$824, E93) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O93" s="19"/>
@@ -17371,7 +17324,7 @@
       <c r="L94" s="19"/>
       <c r="M94" s="19"/>
       <c r="N94" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B94, $C$2:$C$824, C94, $D$2:$D$824, D94, $E$2:$E$824, E94) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17408,7 +17361,7 @@
       <c r="L95" s="19"/>
       <c r="M95" s="19"/>
       <c r="N95" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B95, $C$2:$C$824, C95, $D$2:$D$824, D95, $E$2:$E$824, E95) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O95" s="19"/>
@@ -17446,7 +17399,7 @@
       <c r="L96" s="19"/>
       <c r="M96" s="19"/>
       <c r="N96" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B96, $C$2:$C$824, C96, $D$2:$D$824, D96, $E$2:$E$824, E96) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O96" s="19"/>
@@ -17484,7 +17437,7 @@
       <c r="L97" s="19"/>
       <c r="M97" s="19"/>
       <c r="N97" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B97, $C$2:$C$824, C97, $D$2:$D$824, D97, $E$2:$E$824, E97) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17521,7 +17474,7 @@
       <c r="L98" s="19"/>
       <c r="M98" s="19"/>
       <c r="N98" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B98, $C$2:$C$824, C98, $D$2:$D$824, D98, $E$2:$E$824, E98) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O98" s="19"/>
@@ -17559,7 +17512,7 @@
       <c r="L99" s="19"/>
       <c r="M99" s="19"/>
       <c r="N99" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B99, $C$2:$C$824, C99, $D$2:$D$824, D99, $E$2:$E$824, E99) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17596,7 +17549,7 @@
       <c r="L100" s="19"/>
       <c r="M100" s="19"/>
       <c r="N100" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B100, $C$2:$C$824, C100, $D$2:$D$824, D100, $E$2:$E$824, E100) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O100" s="19"/>
@@ -17634,7 +17587,7 @@
       <c r="L101" s="19"/>
       <c r="M101" s="19"/>
       <c r="N101" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B101, $C$2:$C$824, C101, $D$2:$D$824, D101, $E$2:$E$824, E101) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17673,7 +17626,7 @@
       <c r="L102" s="19"/>
       <c r="M102" s="19"/>
       <c r="N102" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B102, $C$2:$C$824, C102, $D$2:$D$824, D102, $E$2:$E$824, E102) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O102" s="20"/>
@@ -17716,11 +17669,11 @@
         <v>33950</v>
       </c>
       <c r="M103" s="20">
-        <f t="shared" ref="M103:M115" si="0">ABS((D103*E103)-L103)</f>
+        <f t="shared" ref="M103:M115" si="2">ABS((D103*E103)-L103)</f>
         <v>500</v>
       </c>
       <c r="N103" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B103, $C$2:$C$824, C103, $D$2:$D$824, D103, $E$2:$E$824, E103) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17762,11 +17715,11 @@
         <v>20010</v>
       </c>
       <c r="M104" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>450</v>
       </c>
       <c r="N104" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B104, $C$2:$C$824, C104, $D$2:$D$824, D104, $E$2:$E$824, E104) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17808,11 +17761,11 @@
         <v>12600</v>
       </c>
       <c r="M105" s="47">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>200</v>
       </c>
       <c r="N105" s="49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B105, $C$2:$C$824, C105, $D$2:$D$824, D105, $E$2:$E$824, E105) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O105" s="47"/>
@@ -17855,11 +17808,11 @@
         <v>12510</v>
       </c>
       <c r="M106" s="47">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>290</v>
       </c>
       <c r="N106" s="49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B106, $C$2:$C$824, C106, $D$2:$D$824, D106, $E$2:$E$824, E106) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O106" s="47"/>
@@ -17902,11 +17855,11 @@
         <v>14552</v>
       </c>
       <c r="M107" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N107" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B107, $C$2:$C$824, C107, $D$2:$D$824, D107, $E$2:$E$824, E107) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17948,11 +17901,11 @@
         <v>25300</v>
       </c>
       <c r="M108" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>650</v>
       </c>
       <c r="N108" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B108, $C$2:$C$824, C108, $D$2:$D$824, D108, $E$2:$E$824, E108) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -17994,11 +17947,11 @@
         <v>34100</v>
       </c>
       <c r="M109" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>700</v>
       </c>
       <c r="N109" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B109, $C$2:$C$824, C109, $D$2:$D$824, D109, $E$2:$E$824, E109) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O109" s="20"/>
@@ -18041,11 +17994,11 @@
         <v>18800</v>
       </c>
       <c r="M110" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>500</v>
       </c>
       <c r="N110" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B110, $C$2:$C$824, C110, $D$2:$D$824, D110, $E$2:$E$824, E110) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18087,11 +18040,11 @@
         <v>17150</v>
       </c>
       <c r="M111" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N111" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B111, $C$2:$C$824, C111, $D$2:$D$824, D111, $E$2:$E$824, E111) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18133,11 +18086,11 @@
         <v>20260</v>
       </c>
       <c r="M112" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N112" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B112, $C$2:$C$824, C112, $D$2:$D$824, D112, $E$2:$E$824, E112) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18179,11 +18132,11 @@
         <v>10300</v>
       </c>
       <c r="M113" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N113" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B113, $C$2:$C$824, C113, $D$2:$D$824, D113, $E$2:$E$824, E113) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18225,11 +18178,11 @@
         <v>25780</v>
       </c>
       <c r="M114" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N114" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B114, $C$2:$C$824, C114, $D$2:$D$824, D114, $E$2:$E$824, E114) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18271,11 +18224,11 @@
         <v>14440</v>
       </c>
       <c r="M115" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N115" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B115, $C$2:$C$824, C115, $D$2:$D$824, D115, $E$2:$E$824, E115) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18309,7 +18262,7 @@
       </c>
       <c r="J116" s="23"/>
       <c r="N116" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B116, $C$2:$C$824, C116, $D$2:$D$824, D116, $E$2:$E$824, E116) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18343,7 +18296,7 @@
       </c>
       <c r="J117" s="23"/>
       <c r="N117" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B117, $C$2:$C$824, C117, $D$2:$D$824, D117, $E$2:$E$824, E117) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18389,7 +18342,7 @@
         <v>294</v>
       </c>
       <c r="N118" s="48" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B118, $C$2:$C$824, C118, $D$2:$D$824, D118, $E$2:$E$824, E118) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O118" s="47"/>
@@ -18436,7 +18389,7 @@
         <v>294</v>
       </c>
       <c r="N119" s="49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B119, $C$2:$C$824, C119, $D$2:$D$824, D119, $E$2:$E$824, E119) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O119" s="47"/>
@@ -18483,7 +18436,7 @@
         <v>650</v>
       </c>
       <c r="N120" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B120, $C$2:$C$824, C120, $D$2:$D$824, D120, $E$2:$E$824, E120) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18529,7 +18482,7 @@
         <v>765</v>
       </c>
       <c r="N121" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B121, $C$2:$C$824, C121, $D$2:$D$824, D121, $E$2:$E$824, E121) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18565,7 +18518,7 @@
         <v>117</v>
       </c>
       <c r="N122" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B122, $C$2:$C$824, C122, $D$2:$D$824, D122, $E$2:$E$824, E122) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18611,7 +18564,7 @@
         <v>360</v>
       </c>
       <c r="N123" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B123, $C$2:$C$824, C123, $D$2:$D$824, D123, $E$2:$E$824, E123) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18657,7 +18610,7 @@
         <v>525</v>
       </c>
       <c r="N124" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B124, $C$2:$C$824, C124, $D$2:$D$824, D124, $E$2:$E$824, E124) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18703,7 +18656,7 @@
         <v>300</v>
       </c>
       <c r="N125" s="30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B125, $C$2:$C$824, C125, $D$2:$D$824, D125, $E$2:$E$824, E125) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O125" s="33" t="s">
@@ -18752,7 +18705,7 @@
         <v>300</v>
       </c>
       <c r="N126" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B126, $C$2:$C$824, C126, $D$2:$D$824, D126, $E$2:$E$824, E126) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18786,7 +18739,7 @@
       </c>
       <c r="J127" s="23"/>
       <c r="N127" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B127, $C$2:$C$824, C127, $D$2:$D$824, D127, $E$2:$E$824, E127) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O127" s="12"/>
@@ -18826,7 +18779,7 @@
         <v>145</v>
       </c>
       <c r="N128" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B128, $C$2:$C$824, C128, $D$2:$D$824, D128, $E$2:$E$824, E128) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -18872,7 +18825,7 @@
         <v>300</v>
       </c>
       <c r="N129" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B129, $C$2:$C$824, C129, $D$2:$D$824, D129, $E$2:$E$824, E129) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O129" s="20"/>
@@ -18919,7 +18872,7 @@
         <v>300</v>
       </c>
       <c r="N130" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B130, $C$2:$C$824, C130, $D$2:$D$824, D130, $E$2:$E$824, E130) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N130:N193" si="3">IF(COUNTIFS( $B$2:$B$824, B130, $C$2:$C$824, C130, $D$2:$D$824, D130, $E$2:$E$824, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -18965,7 +18918,7 @@
         <v>340</v>
       </c>
       <c r="N131" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B131, $C$2:$C$824, C131, $D$2:$D$824, D131, $E$2:$E$824, E131) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19011,7 +18964,7 @@
         <v>175</v>
       </c>
       <c r="N132" s="49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B132, $C$2:$C$824, C132, $D$2:$D$824, D132, $E$2:$E$824, E132) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Duplicate</v>
       </c>
       <c r="O132" s="47"/>
@@ -19058,7 +19011,7 @@
         <v>225</v>
       </c>
       <c r="N133" s="48" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B133, $C$2:$C$824, C133, $D$2:$D$824, D133, $E$2:$E$824, E133) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Duplicate</v>
       </c>
       <c r="O133" s="47"/>
@@ -19096,7 +19049,7 @@
       <c r="L134" s="20"/>
       <c r="M134" s="20"/>
       <c r="N134" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B134, $C$2:$C$824, C134, $D$2:$D$824, D134, $E$2:$E$824, E134) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O134" s="20"/>
@@ -19143,7 +19096,7 @@
         <v>300</v>
       </c>
       <c r="N135" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B135, $C$2:$C$824, C135, $D$2:$D$824, D135, $E$2:$E$824, E135) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O135" s="20"/>
@@ -19190,7 +19143,7 @@
         <v>1567.5</v>
       </c>
       <c r="N136" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B136, $C$2:$C$824, C136, $D$2:$D$824, D136, $E$2:$E$824, E136) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O136" s="20"/>
@@ -19237,7 +19190,7 @@
         <v>300</v>
       </c>
       <c r="N137" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B137, $C$2:$C$824, C137, $D$2:$D$824, D137, $E$2:$E$824, E137) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O137" s="20"/>
@@ -19284,7 +19237,7 @@
         <v>300</v>
       </c>
       <c r="N138" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B138, $C$2:$C$824, C138, $D$2:$D$824, D138, $E$2:$E$824, E138) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O138" s="20"/>
@@ -19324,7 +19277,7 @@
       <c r="L139" s="20"/>
       <c r="M139" s="20"/>
       <c r="N139" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B139, $C$2:$C$824, C139, $D$2:$D$824, D139, $E$2:$E$824, E139) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O139" s="20"/>
@@ -19371,7 +19324,7 @@
         <v>300</v>
       </c>
       <c r="N140" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B140, $C$2:$C$824, C140, $D$2:$D$824, D140, $E$2:$E$824, E140) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O140" s="20"/>
@@ -19418,7 +19371,7 @@
         <v>300</v>
       </c>
       <c r="N141" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B141, $C$2:$C$824, C141, $D$2:$D$824, D141, $E$2:$E$824, E141) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19455,7 +19408,7 @@
       <c r="L142" s="20"/>
       <c r="M142" s="20"/>
       <c r="N142" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B142, $C$2:$C$824, C142, $D$2:$D$824, D142, $E$2:$E$824, E142) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O142" s="12"/>
@@ -19502,7 +19455,7 @@
         <v>270</v>
       </c>
       <c r="N143" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B143, $C$2:$C$824, C143, $D$2:$D$824, D143, $E$2:$E$824, E143) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O143" s="20"/>
@@ -19549,7 +19502,7 @@
         <v>430</v>
       </c>
       <c r="N144" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B144, $C$2:$C$824, C144, $D$2:$D$824, D144, $E$2:$E$824, E144) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19595,7 +19548,7 @@
         <v>275</v>
       </c>
       <c r="N145" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B145, $C$2:$C$824, C145, $D$2:$D$824, D145, $E$2:$E$824, E145) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19631,7 +19584,7 @@
         <v>55</v>
       </c>
       <c r="N146" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B146, $C$2:$C$824, C146, $D$2:$D$824, D146, $E$2:$E$824, E146) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19672,7 +19625,7 @@
       <c r="L147" s="19"/>
       <c r="M147" s="19"/>
       <c r="N147" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B147, $C$2:$C$824, C147, $D$2:$D$824, D147, $E$2:$E$824, E147) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O147" s="20"/>
@@ -19719,7 +19672,7 @@
         <v>400</v>
       </c>
       <c r="N148" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B148, $C$2:$C$824, C148, $D$2:$D$824, D148, $E$2:$E$824, E148) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O148" s="20"/>
@@ -19756,7 +19709,7 @@
         <v>117</v>
       </c>
       <c r="N149" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B149, $C$2:$C$824, C149, $D$2:$D$824, D149, $E$2:$E$824, E149) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O149" s="12"/>
@@ -19793,7 +19746,7 @@
         <v>118</v>
       </c>
       <c r="N150" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B150, $C$2:$C$824, C150, $D$2:$D$824, D150, $E$2:$E$824, E150) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O150" s="12"/>
@@ -19840,7 +19793,7 @@
         <v>800</v>
       </c>
       <c r="N151" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B151, $C$2:$C$824, C151, $D$2:$D$824, D151, $E$2:$E$824, E151) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19886,7 +19839,7 @@
         <v>260</v>
       </c>
       <c r="N152" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B152, $C$2:$C$824, C152, $D$2:$D$824, D152, $E$2:$E$824, E152) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -19920,7 +19873,7 @@
       </c>
       <c r="J153" s="54"/>
       <c r="N153" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B153, $C$2:$C$824, C153, $D$2:$D$824, D153, $E$2:$E$824, E153) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O153" s="12"/>
@@ -19967,7 +19920,7 @@
         <v>527.5</v>
       </c>
       <c r="N154" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B154, $C$2:$C$824, C154, $D$2:$D$824, D154, $E$2:$E$824, E154) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20006,7 +19959,7 @@
         <v>143</v>
       </c>
       <c r="N155" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B155, $C$2:$C$824, C155, $D$2:$D$824, D155, $E$2:$E$824, E155) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20042,7 +19995,7 @@
         <v>41</v>
       </c>
       <c r="N156" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B156, $C$2:$C$824, C156, $D$2:$D$824, D156, $E$2:$E$824, E156) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20078,7 +20031,7 @@
         <v>41</v>
       </c>
       <c r="N157" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B157, $C$2:$C$824, C157, $D$2:$D$824, D157, $E$2:$E$824, E157) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O157" s="12"/>
@@ -20125,7 +20078,7 @@
         <v>650</v>
       </c>
       <c r="N158" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B158, $C$2:$C$824, C158, $D$2:$D$824, D158, $E$2:$E$824, E158) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20159,7 +20112,7 @@
       </c>
       <c r="J159" s="54"/>
       <c r="N159" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B159, $C$2:$C$824, C159, $D$2:$D$824, D159, $E$2:$E$824, E159) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O159" s="12"/>
@@ -20196,7 +20149,7 @@
         <v>204</v>
       </c>
       <c r="N160" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B160, $C$2:$C$824, C160, $D$2:$D$824, D160, $E$2:$E$824, E160) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O160" s="12"/>
@@ -20233,7 +20186,7 @@
         <v>117</v>
       </c>
       <c r="N161" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B161, $C$2:$C$824, C161, $D$2:$D$824, D161, $E$2:$E$824, E161) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O161" s="12"/>
@@ -20270,7 +20223,7 @@
         <v>156</v>
       </c>
       <c r="N162" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B162, $C$2:$C$824, C162, $D$2:$D$824, D162, $E$2:$E$824, E162) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20306,7 +20259,7 @@
         <v>118</v>
       </c>
       <c r="N163" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B163, $C$2:$C$824, C163, $D$2:$D$824, D163, $E$2:$E$824, E163) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20352,7 +20305,7 @@
         <v>650</v>
       </c>
       <c r="N164" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B164, $C$2:$C$824, C164, $D$2:$D$824, D164, $E$2:$E$824, E164) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20398,7 +20351,7 @@
         <v>150</v>
       </c>
       <c r="N165" s="48" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B165, $C$2:$C$824, C165, $D$2:$D$824, D165, $E$2:$E$824, E165) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Duplicate</v>
       </c>
       <c r="O165" s="47"/>
@@ -20445,7 +20398,7 @@
         <v>250</v>
       </c>
       <c r="N166" s="49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B166, $C$2:$C$824, C166, $D$2:$D$824, D166, $E$2:$E$824, E166) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Duplicate</v>
       </c>
       <c r="O166" s="47"/>
@@ -20480,7 +20433,7 @@
       </c>
       <c r="J167" s="54"/>
       <c r="N167" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B167, $C$2:$C$824, C167, $D$2:$D$824, D167, $E$2:$E$824, E167) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O167" s="12"/>
@@ -20527,7 +20480,7 @@
         <v>700</v>
       </c>
       <c r="N168" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B168, $C$2:$C$824, C168, $D$2:$D$824, D168, $E$2:$E$824, E168) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20573,7 +20526,7 @@
         <v>250</v>
       </c>
       <c r="N169" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B169, $C$2:$C$824, C169, $D$2:$D$824, D169, $E$2:$E$824, E169) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20619,7 +20572,7 @@
         <v>300</v>
       </c>
       <c r="N170" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B170, $C$2:$C$824, C170, $D$2:$D$824, D170, $E$2:$E$824, E170) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20665,7 +20618,7 @@
         <v>370</v>
       </c>
       <c r="N171" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B171, $C$2:$C$824, C171, $D$2:$D$824, D171, $E$2:$E$824, E171) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20711,7 +20664,7 @@
         <v>285</v>
       </c>
       <c r="N172" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B172, $C$2:$C$824, C172, $D$2:$D$824, D172, $E$2:$E$824, E172) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20745,7 +20698,7 @@
       </c>
       <c r="J173" s="54"/>
       <c r="N173" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B173, $C$2:$C$824, C173, $D$2:$D$824, D173, $E$2:$E$824, E173) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20781,7 +20734,7 @@
         <v>118</v>
       </c>
       <c r="N174" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B174, $C$2:$C$824, C174, $D$2:$D$824, D174, $E$2:$E$824, E174) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O174" s="12"/>
@@ -20828,7 +20781,7 @@
         <v>250</v>
       </c>
       <c r="N175" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B175, $C$2:$C$824, C175, $D$2:$D$824, D175, $E$2:$E$824, E175) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20874,7 +20827,7 @@
         <v>726</v>
       </c>
       <c r="N176" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B176, $C$2:$C$824, C176, $D$2:$D$824, D176, $E$2:$E$824, E176) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -20910,7 +20863,7 @@
         <v>118</v>
       </c>
       <c r="N177" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B177, $C$2:$C$824, C177, $D$2:$D$824, D177, $E$2:$E$824, E177) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O177" s="12"/>
@@ -20945,7 +20898,7 @@
       </c>
       <c r="J178" s="54"/>
       <c r="N178" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B178, $C$2:$C$824, C178, $D$2:$D$824, D178, $E$2:$E$824, E178) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O178" s="12"/>
@@ -20982,7 +20935,7 @@
         <v>118</v>
       </c>
       <c r="N179" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B179, $C$2:$C$824, C179, $D$2:$D$824, D179, $E$2:$E$824, E179) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O179" s="12"/>
@@ -21019,7 +20972,7 @@
         <v>117</v>
       </c>
       <c r="N180" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B180, $C$2:$C$824, C180, $D$2:$D$824, D180, $E$2:$E$824, E180) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O180" s="12"/>
@@ -21054,7 +21007,7 @@
       </c>
       <c r="J181" s="54"/>
       <c r="N181" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B181, $C$2:$C$824, C181, $D$2:$D$824, D181, $E$2:$E$824, E181) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21090,7 +21043,7 @@
         <v>118</v>
       </c>
       <c r="N182" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B182, $C$2:$C$824, C182, $D$2:$D$824, D182, $E$2:$E$824, E182) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21126,7 +21079,7 @@
         <v>118</v>
       </c>
       <c r="N183" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B183, $C$2:$C$824, C183, $D$2:$D$824, D183, $E$2:$E$824, E183) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O183" s="12"/>
@@ -21163,7 +21116,7 @@
         <v>117</v>
       </c>
       <c r="N184" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B184, $C$2:$C$824, C184, $D$2:$D$824, D184, $E$2:$E$824, E184) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O184" s="12"/>
@@ -21198,7 +21151,7 @@
       </c>
       <c r="J185" s="54"/>
       <c r="N185" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B185, $C$2:$C$824, C185, $D$2:$D$824, D185, $E$2:$E$824, E185) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21244,7 +21197,7 @@
         <v>501</v>
       </c>
       <c r="N186" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B186, $C$2:$C$824, C186, $D$2:$D$824, D186, $E$2:$E$824, E186) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21278,7 +21231,7 @@
       </c>
       <c r="J187" s="54"/>
       <c r="N187" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B187, $C$2:$C$824, C187, $D$2:$D$824, D187, $E$2:$E$824, E187) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O187" s="12"/>
@@ -21325,7 +21278,7 @@
         <v>300</v>
       </c>
       <c r="N188" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B188, $C$2:$C$824, C188, $D$2:$D$824, D188, $E$2:$E$824, E188) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21371,7 +21324,7 @@
         <v>540</v>
       </c>
       <c r="N189" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B189, $C$2:$C$824, C189, $D$2:$D$824, D189, $E$2:$E$824, E189) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21417,7 +21370,7 @@
         <v>650</v>
       </c>
       <c r="N190" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B190, $C$2:$C$824, C190, $D$2:$D$824, D190, $E$2:$E$824, E190) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21463,7 +21416,7 @@
         <v>275</v>
       </c>
       <c r="N191" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B191, $C$2:$C$824, C191, $D$2:$D$824, D191, $E$2:$E$824, E191) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21499,7 +21452,7 @@
         <v>118</v>
       </c>
       <c r="N192" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B192, $C$2:$C$824, C192, $D$2:$D$824, D192, $E$2:$E$824, E192) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
       <c r="O192" s="12"/>
@@ -21546,7 +21499,7 @@
         <v>300</v>
       </c>
       <c r="N193" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B193, $C$2:$C$824, C193, $D$2:$D$824, D193, $E$2:$E$824, E193) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="3"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21592,7 +21545,7 @@
         <v>320</v>
       </c>
       <c r="N194" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B194, $C$2:$C$824, C194, $D$2:$D$824, D194, $E$2:$E$824, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N194:N257" si="4">IF(COUNTIFS( $B$2:$B$824, B194, $C$2:$C$824, C194, $D$2:$D$824, D194, $E$2:$E$824, E194) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -21638,7 +21591,7 @@
         <v>448</v>
       </c>
       <c r="N195" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B195, $C$2:$C$824, C195, $D$2:$D$824, D195, $E$2:$E$824, E195) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21672,7 +21625,7 @@
       </c>
       <c r="J196" s="54"/>
       <c r="N196" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B196, $C$2:$C$824, C196, $D$2:$D$824, D196, $E$2:$E$824, E196) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O196" s="12"/>
@@ -21707,7 +21660,7 @@
       </c>
       <c r="J197" s="54"/>
       <c r="N197" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B197, $C$2:$C$824, C197, $D$2:$D$824, D197, $E$2:$E$824, E197) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O197" s="12"/>
@@ -21744,7 +21697,7 @@
         <v>118</v>
       </c>
       <c r="N198" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B198, $C$2:$C$824, C198, $D$2:$D$824, D198, $E$2:$E$824, E198) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O198" s="12"/>
@@ -21784,7 +21737,7 @@
         <v>144</v>
       </c>
       <c r="N199" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B199, $C$2:$C$824, C199, $D$2:$D$824, D199, $E$2:$E$824, E199) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O199" s="12"/>
@@ -21821,7 +21774,7 @@
         <v>55</v>
       </c>
       <c r="N200" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B200, $C$2:$C$824, C200, $D$2:$D$824, D200, $E$2:$E$824, E200) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21867,7 +21820,7 @@
         <v>300</v>
       </c>
       <c r="N201" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B201, $C$2:$C$824, C201, $D$2:$D$824, D201, $E$2:$E$824, E201) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21913,7 +21866,7 @@
         <v>188</v>
       </c>
       <c r="N202" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B202, $C$2:$C$824, C202, $D$2:$D$824, D202, $E$2:$E$824, E202) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21959,7 +21912,7 @@
         <v>250</v>
       </c>
       <c r="N203" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B203, $C$2:$C$824, C203, $D$2:$D$824, D203, $E$2:$E$824, E203) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22005,7 +21958,7 @@
         <v>500</v>
       </c>
       <c r="N204" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B204, $C$2:$C$824, C204, $D$2:$D$824, D204, $E$2:$E$824, E204) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22041,7 +21994,7 @@
         <v>118</v>
       </c>
       <c r="N205" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B205, $C$2:$C$824, C205, $D$2:$D$824, D205, $E$2:$E$824, E205) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O205" s="12"/>
@@ -22076,7 +22029,7 @@
       </c>
       <c r="J206" s="54"/>
       <c r="N206" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B206, $C$2:$C$824, C206, $D$2:$D$824, D206, $E$2:$E$824, E206) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O206" s="12"/>
@@ -22123,7 +22076,7 @@
         <v>140</v>
       </c>
       <c r="N207" s="49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B207, $C$2:$C$824, C207, $D$2:$D$824, D207, $E$2:$E$824, E207) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Duplicate</v>
       </c>
       <c r="O207" s="47"/>
@@ -22170,7 +22123,7 @@
         <v>300</v>
       </c>
       <c r="N208" s="49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B208, $C$2:$C$824, C208, $D$2:$D$824, D208, $E$2:$E$824, E208) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Duplicate</v>
       </c>
       <c r="O208" s="47"/>
@@ -22217,7 +22170,7 @@
         <v>260</v>
       </c>
       <c r="N209" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B209, $C$2:$C$824, C209, $D$2:$D$824, D209, $E$2:$E$824, E209) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22251,7 +22204,7 @@
       </c>
       <c r="J210" s="54"/>
       <c r="N210" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B210, $C$2:$C$824, C210, $D$2:$D$824, D210, $E$2:$E$824, E210) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O210" s="12"/>
@@ -22298,7 +22251,7 @@
         <v>300</v>
       </c>
       <c r="N211" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B211, $C$2:$C$824, C211, $D$2:$D$824, D211, $E$2:$E$824, E211) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22334,7 +22287,7 @@
         <v>117</v>
       </c>
       <c r="N212" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B212, $C$2:$C$824, C212, $D$2:$D$824, D212, $E$2:$E$824, E212) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O212" s="12"/>
@@ -22369,7 +22322,7 @@
       </c>
       <c r="J213" s="54"/>
       <c r="N213" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B213, $C$2:$C$824, C213, $D$2:$D$824, D213, $E$2:$E$824, E213) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O213" s="12"/>
@@ -22406,7 +22359,7 @@
         <v>117</v>
       </c>
       <c r="N214" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B214, $C$2:$C$824, C214, $D$2:$D$824, D214, $E$2:$E$824, E214) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22452,7 +22405,7 @@
         <v>500</v>
       </c>
       <c r="N215" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B215, $C$2:$C$824, C215, $D$2:$D$824, D215, $E$2:$E$824, E215) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22498,7 +22451,7 @@
         <v>650</v>
       </c>
       <c r="N216" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B216, $C$2:$C$824, C216, $D$2:$D$824, D216, $E$2:$E$824, E216) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22534,7 +22487,7 @@
         <v>118</v>
       </c>
       <c r="N217" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B217, $C$2:$C$824, C217, $D$2:$D$824, D217, $E$2:$E$824, E217) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O217" s="12"/>
@@ -22569,7 +22522,7 @@
       </c>
       <c r="J218" s="54"/>
       <c r="N218" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B218, $C$2:$C$824, C218, $D$2:$D$824, D218, $E$2:$E$824, E218) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O218" s="12"/>
@@ -22616,7 +22569,7 @@
         <v>300</v>
       </c>
       <c r="N219" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B219, $C$2:$C$824, C219, $D$2:$D$824, D219, $E$2:$E$824, E219) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O219" s="20"/>
@@ -22653,7 +22606,7 @@
         <v>55</v>
       </c>
       <c r="N220" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B220, $C$2:$C$824, C220, $D$2:$D$824, D220, $E$2:$E$824, E220) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22687,7 +22640,7 @@
       </c>
       <c r="J221" s="54"/>
       <c r="N221" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B221, $C$2:$C$824, C221, $D$2:$D$824, D221, $E$2:$E$824, E221) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22721,7 +22674,7 @@
       </c>
       <c r="J222" s="54"/>
       <c r="N222" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B222, $C$2:$C$824, C222, $D$2:$D$824, D222, $E$2:$E$824, E222) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O222" s="12"/>
@@ -22756,7 +22709,7 @@
       </c>
       <c r="J223" s="54"/>
       <c r="N223" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B223, $C$2:$C$824, C223, $D$2:$D$824, D223, $E$2:$E$824, E223) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O223" s="12"/>
@@ -22791,7 +22744,7 @@
       </c>
       <c r="J224" s="54"/>
       <c r="N224" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B224, $C$2:$C$824, C224, $D$2:$D$824, D224, $E$2:$E$824, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O224" s="12"/>
@@ -22826,7 +22779,7 @@
       </c>
       <c r="J225" s="54"/>
       <c r="N225" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B225, $C$2:$C$824, C225, $D$2:$D$824, D225, $E$2:$E$824, E225) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O225" s="12"/>
@@ -22861,7 +22814,7 @@
       </c>
       <c r="J226" s="54"/>
       <c r="N226" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B226, $C$2:$C$824, C226, $D$2:$D$824, D226, $E$2:$E$824, E226) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O226" s="12"/>
@@ -22908,7 +22861,7 @@
         <v>700</v>
       </c>
       <c r="N227" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B227, $C$2:$C$824, C227, $D$2:$D$824, D227, $E$2:$E$824, E227) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22947,7 +22900,7 @@
         <v>146</v>
       </c>
       <c r="N228" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B228, $C$2:$C$824, C228, $D$2:$D$824, D228, $E$2:$E$824, E228) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22981,7 +22934,7 @@
       </c>
       <c r="J229" s="54"/>
       <c r="N229" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B229, $C$2:$C$824, C229, $D$2:$D$824, D229, $E$2:$E$824, E229) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O229" s="12"/>
@@ -23016,7 +22969,7 @@
       </c>
       <c r="J230" s="54"/>
       <c r="N230" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B230, $C$2:$C$824, C230, $D$2:$D$824, D230, $E$2:$E$824, E230) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O230" s="12"/>
@@ -23053,7 +23006,7 @@
         <v>118</v>
       </c>
       <c r="N231" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B231, $C$2:$C$824, C231, $D$2:$D$824, D231, $E$2:$E$824, E231) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O231" s="12"/>
@@ -23088,7 +23041,7 @@
       </c>
       <c r="J232" s="54"/>
       <c r="N232" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B232, $C$2:$C$824, C232, $D$2:$D$824, D232, $E$2:$E$824, E232) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23134,7 +23087,7 @@
         <v>650</v>
       </c>
       <c r="N233" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B233, $C$2:$C$824, C233, $D$2:$D$824, D233, $E$2:$E$824, E233) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23180,7 +23133,7 @@
         <v>250</v>
       </c>
       <c r="N234" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B234, $C$2:$C$824, C234, $D$2:$D$824, D234, $E$2:$E$824, E234) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23214,7 +23167,7 @@
       </c>
       <c r="J235" s="54"/>
       <c r="N235" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B235, $C$2:$C$824, C235, $D$2:$D$824, D235, $E$2:$E$824, E235) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O235" s="12"/>
@@ -23261,7 +23214,7 @@
         <v>480</v>
       </c>
       <c r="N236" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B236, $C$2:$C$824, C236, $D$2:$D$824, D236, $E$2:$E$824, E236) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23297,7 +23250,7 @@
         <v>118</v>
       </c>
       <c r="N237" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B237, $C$2:$C$824, C237, $D$2:$D$824, D237, $E$2:$E$824, E237) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O237" s="12"/>
@@ -23332,7 +23285,7 @@
       </c>
       <c r="J238" s="23"/>
       <c r="N238" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B238, $C$2:$C$824, C238, $D$2:$D$824, D238, $E$2:$E$824, E238) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23366,7 +23319,7 @@
       </c>
       <c r="J239" s="54"/>
       <c r="N239" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B239, $C$2:$C$824, C239, $D$2:$D$824, D239, $E$2:$E$824, E239) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23405,7 +23358,7 @@
       <c r="L240" s="20"/>
       <c r="M240" s="20"/>
       <c r="N240" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B240, $C$2:$C$824, C240, $D$2:$D$824, D240, $E$2:$E$824, E240) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O240" s="20"/>
@@ -23440,7 +23393,7 @@
       </c>
       <c r="J241" s="54"/>
       <c r="N241" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B241, $C$2:$C$824, C241, $D$2:$D$824, D241, $E$2:$E$824, E241) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O241" s="19"/>
@@ -23487,7 +23440,7 @@
         <v>1000</v>
       </c>
       <c r="N242" s="38" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B242, $C$2:$C$824, C242, $D$2:$D$824, D242, $E$2:$E$824, E242) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O242" s="37"/>
@@ -23522,7 +23475,7 @@
       </c>
       <c r="J243" s="54"/>
       <c r="N243" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B243, $C$2:$C$824, C243, $D$2:$D$824, D243, $E$2:$E$824, E243) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O243" s="12"/>
@@ -23557,7 +23510,7 @@
       </c>
       <c r="J244" s="54"/>
       <c r="N244" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B244, $C$2:$C$824, C244, $D$2:$D$824, D244, $E$2:$E$824, E244) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O244" s="12"/>
@@ -23594,7 +23547,7 @@
         <v>117</v>
       </c>
       <c r="N245" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B245, $C$2:$C$824, C245, $D$2:$D$824, D245, $E$2:$E$824, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O245" s="12"/>
@@ -23641,7 +23594,7 @@
         <v>300</v>
       </c>
       <c r="N246" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B246, $C$2:$C$824, C246, $D$2:$D$824, D246, $E$2:$E$824, E246) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23675,7 +23628,7 @@
       </c>
       <c r="J247" s="54"/>
       <c r="N247" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B247, $C$2:$C$824, C247, $D$2:$D$824, D247, $E$2:$E$824, E247) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O247" s="12"/>
@@ -23715,7 +23668,7 @@
       <c r="L248" s="20"/>
       <c r="M248" s="20"/>
       <c r="N248" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B248, $C$2:$C$824, C248, $D$2:$D$824, D248, $E$2:$E$824, E248) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O248" s="19"/>
@@ -23762,7 +23715,7 @@
         <v>940</v>
       </c>
       <c r="N249" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B249, $C$2:$C$824, C249, $D$2:$D$824, D249, $E$2:$E$824, E249) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23798,7 +23751,7 @@
         <v>55</v>
       </c>
       <c r="N250" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B250, $C$2:$C$824, C250, $D$2:$D$824, D250, $E$2:$E$824, E250) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O250" s="12"/>
@@ -23833,7 +23786,7 @@
       </c>
       <c r="J251" s="54"/>
       <c r="N251" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B251, $C$2:$C$824, C251, $D$2:$D$824, D251, $E$2:$E$824, E251) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O251" s="19"/>
@@ -23868,7 +23821,7 @@
       </c>
       <c r="J252" s="54"/>
       <c r="N252" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B252, $C$2:$C$824, C252, $D$2:$D$824, D252, $E$2:$E$824, E252) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O252" s="12"/>
@@ -23915,7 +23868,7 @@
         <v>650</v>
       </c>
       <c r="N253" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B253, $C$2:$C$824, C253, $D$2:$D$824, D253, $E$2:$E$824, E253) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O253" s="20"/>
@@ -23953,7 +23906,7 @@
       <c r="L254" s="20"/>
       <c r="M254" s="20"/>
       <c r="N254" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B254, $C$2:$C$824, C254, $D$2:$D$824, D254, $E$2:$E$824, E254) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O254" s="12"/>
@@ -23990,7 +23943,7 @@
         <v>118</v>
       </c>
       <c r="N255" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B255, $C$2:$C$824, C255, $D$2:$D$824, D255, $E$2:$E$824, E255) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O255" s="12"/>
@@ -24027,7 +23980,7 @@
         <v>118</v>
       </c>
       <c r="N256" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B256, $C$2:$C$824, C256, $D$2:$D$824, D256, $E$2:$E$824, E256) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O256" s="19"/>
@@ -24064,7 +24017,7 @@
         <v>118</v>
       </c>
       <c r="N257" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B257, $C$2:$C$824, C257, $D$2:$D$824, D257, $E$2:$E$824, E257) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24098,7 +24051,7 @@
       </c>
       <c r="J258" s="54"/>
       <c r="N258" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B258, $C$2:$C$824, C258, $D$2:$D$824, D258, $E$2:$E$824, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N258:N284" si="5">IF(COUNTIFS( $B$2:$B$824, B258, $C$2:$C$824, C258, $D$2:$D$824, D258, $E$2:$E$824, E258) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -24144,7 +24097,7 @@
         <v>250</v>
       </c>
       <c r="N259" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B259, $C$2:$C$824, C259, $D$2:$D$824, D259, $E$2:$E$824, E259) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24178,7 +24131,7 @@
       </c>
       <c r="J260" s="54"/>
       <c r="N260" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B260, $C$2:$C$824, C260, $D$2:$D$824, D260, $E$2:$E$824, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O260" s="19"/>
@@ -24213,7 +24166,7 @@
       </c>
       <c r="J261" s="54"/>
       <c r="N261" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B261, $C$2:$C$824, C261, $D$2:$D$824, D261, $E$2:$E$824, E261) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O261" s="19"/>
@@ -24248,7 +24201,7 @@
       </c>
       <c r="J262" s="54"/>
       <c r="N262" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B262, $C$2:$C$824, C262, $D$2:$D$824, D262, $E$2:$E$824, E262) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O262" s="19"/>
@@ -24283,7 +24236,7 @@
       </c>
       <c r="J263" s="54"/>
       <c r="N263" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B263, $C$2:$C$824, C263, $D$2:$D$824, D263, $E$2:$E$824, E263) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O263" s="19"/>
@@ -24318,7 +24271,7 @@
       </c>
       <c r="J264" s="54"/>
       <c r="N264" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B264, $C$2:$C$824, C264, $D$2:$D$824, D264, $E$2:$E$824, E264) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O264" s="19"/>
@@ -24359,7 +24312,7 @@
         <v>3156</v>
       </c>
       <c r="N265" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B265, $C$2:$C$824, C265, $D$2:$D$824, D265, $E$2:$E$824, E265) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24391,11 +24344,11 @@
         <v>4120</v>
       </c>
       <c r="M266" s="20">
-        <f t="shared" ref="M266:M284" si="1">ABS((D266*E266)-L266)</f>
+        <f t="shared" ref="M266:M284" si="6">ABS((D266*E266)-L266)</f>
         <v>270</v>
       </c>
       <c r="N266" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B266, $C$2:$C$824, C266, $D$2:$D$824, D266, $E$2:$E$824, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24427,11 +24380,11 @@
         <v>32900</v>
       </c>
       <c r="M267" s="20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>1000</v>
       </c>
       <c r="N267" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B267, $C$2:$C$824, C267, $D$2:$D$824, D267, $E$2:$E$824, E267) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -24463,11 +24416,11 @@
         <v>4968</v>
       </c>
       <c r="M268" s="20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>280</v>
       </c>
       <c r="N268" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B268, $C$2:$C$824, C268, $D$2:$D$824, D268, $E$2:$E$824, E268) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24499,11 +24452,11 @@
         <v>3005</v>
       </c>
       <c r="M269" s="20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>240</v>
       </c>
       <c r="N269" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B269, $C$2:$C$824, C269, $D$2:$D$824, D269, $E$2:$E$824, E269) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24535,11 +24488,11 @@
         <v>33200</v>
       </c>
       <c r="M270" s="20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>700</v>
       </c>
       <c r="N270" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B270, $C$2:$C$824, C270, $D$2:$D$824, D270, $E$2:$E$824, E270) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -24565,7 +24518,7 @@
         <v>117</v>
       </c>
       <c r="N271" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B271, $C$2:$C$824, C271, $D$2:$D$824, D271, $E$2:$E$824, E271) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24591,7 +24544,7 @@
         <v>117</v>
       </c>
       <c r="N272" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B272, $C$2:$C$824, C272, $D$2:$D$824, D272, $E$2:$E$824, E272) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24623,11 +24576,11 @@
         <v>4080</v>
       </c>
       <c r="M273" s="20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N273" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B273, $C$2:$C$824, C273, $D$2:$D$824, D273, $E$2:$E$824, E273) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24659,11 +24612,11 @@
         <v>8220</v>
       </c>
       <c r="M274" s="20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>360</v>
       </c>
       <c r="N274" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B274, $C$2:$C$824, C274, $D$2:$D$824, D274, $E$2:$E$824, E274) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24695,11 +24648,11 @@
         <v>17400</v>
       </c>
       <c r="M275" s="20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>520</v>
       </c>
       <c r="N275" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B275, $C$2:$C$824, C275, $D$2:$D$824, D275, $E$2:$E$824, E275) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24731,11 +24684,11 @@
         <v>5755</v>
       </c>
       <c r="M276" s="47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>275</v>
       </c>
       <c r="N276" s="49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B276, $C$2:$C$824, C276, $D$2:$D$824, D276, $E$2:$E$824, E276) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O276" s="47"/>
@@ -24762,7 +24715,7 @@
         <v>117</v>
       </c>
       <c r="N277" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B277, $C$2:$C$824, C277, $D$2:$D$824, D277, $E$2:$E$824, E277) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24794,11 +24747,11 @@
         <v>12480</v>
       </c>
       <c r="M278" s="20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>495</v>
       </c>
       <c r="N278" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B278, $C$2:$C$824, C278, $D$2:$D$824, D278, $E$2:$E$824, E278) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24830,11 +24783,11 @@
         <v>16755</v>
       </c>
       <c r="M279" s="20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>295</v>
       </c>
       <c r="N279" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B279, $C$2:$C$824, C279, $D$2:$D$824, D279, $E$2:$E$824, E279) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24866,11 +24819,11 @@
         <v>9270</v>
       </c>
       <c r="M280" s="20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N280" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B280, $C$2:$C$824, C280, $D$2:$D$824, D280, $E$2:$E$824, E280) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24902,11 +24855,11 @@
         <v>5805</v>
       </c>
       <c r="M281" s="47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>225</v>
       </c>
       <c r="N281" s="49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B281, $C$2:$C$824, C281, $D$2:$D$824, D281, $E$2:$E$824, E281) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O281" s="47"/>
@@ -24939,11 +24892,11 @@
         <v>8625</v>
       </c>
       <c r="M282" s="20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>375</v>
       </c>
       <c r="N282" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B282, $C$2:$C$824, C282, $D$2:$D$824, D282, $E$2:$E$824, E282) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24975,11 +24928,11 @@
         <v>6420</v>
       </c>
       <c r="M283" s="20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>460</v>
       </c>
       <c r="N283" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B283, $C$2:$C$824, C283, $D$2:$D$824, D283, $E$2:$E$824, E283) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25011,11 +24964,11 @@
         <v>20350</v>
       </c>
       <c r="M284" s="20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N284" s="12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$824, B284, $C$2:$C$824, C284, $D$2:$D$824, D284, $E$2:$E$824, E284) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
